--- a/PARA EL RETIRO/ACCESOS VARIOS.xlsx
+++ b/PARA EL RETIRO/ACCESOS VARIOS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/PARA EL RETIRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="961" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A794DB26-F4D3-4E21-93E0-0D8EF5CBF403}"/>
+  <xr:revisionPtr revIDLastSave="1092" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA08F124-61B3-42AB-88AD-1B813EA39703}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
   </bookViews>
   <sheets>
-    <sheet name="ACCESS" sheetId="1" r:id="rId1"/>
-    <sheet name="ZARKIN" sheetId="2" r:id="rId2"/>
-    <sheet name="ITEKNIA" sheetId="3" r:id="rId3"/>
-    <sheet name="VMA" sheetId="4" r:id="rId4"/>
+    <sheet name="FECHAS" sheetId="1" r:id="rId1"/>
+    <sheet name="VMA" sheetId="4" r:id="rId2"/>
+    <sheet name="ZARKIN" sheetId="2" r:id="rId3"/>
+    <sheet name="ITEKNIA" sheetId="3" r:id="rId4"/>
     <sheet name="VARIAS" sheetId="6" r:id="rId5"/>
     <sheet name="YOLANDA" sheetId="5" r:id="rId6"/>
   </sheets>
@@ -25,22 +25,22 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ACCESS!$B$6:$H$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ITEKNIA!$B$6:$H$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">VMA!$B$6:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ITEKNIA!$B$6:$H$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VMA!$B$6:$H$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">YOLANDA!$B$6:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ZARKIN!$B$6:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$19</definedName>
     <definedName name="BANCOS" localSheetId="0">[1]CATEGORIAS!$C$8:$C$20</definedName>
+    <definedName name="BANCOS" localSheetId="3">[1]CATEGORIAS!$C$8:$C$20</definedName>
+    <definedName name="BANCOS" localSheetId="1">[1]CATEGORIAS!$C$8:$C$20</definedName>
+    <definedName name="BANCOS" localSheetId="5">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="2">[1]CATEGORIAS!$C$8:$C$20</definedName>
-    <definedName name="BANCOS" localSheetId="3">[1]CATEGORIAS!$C$8:$C$20</definedName>
-    <definedName name="BANCOS" localSheetId="5">[1]CATEGORIAS!$C$8:$C$20</definedName>
-    <definedName name="BANCOS" localSheetId="1">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS">[2]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="CATEGORIA" localSheetId="0">[1]CATEGORIAS!$B$6:$L$6</definedName>
+    <definedName name="CATEGORIA" localSheetId="3">[1]CATEGORIAS!$B$6:$L$6</definedName>
+    <definedName name="CATEGORIA" localSheetId="1">[1]CATEGORIAS!$B$6:$L$6</definedName>
+    <definedName name="CATEGORIA" localSheetId="5">[1]CATEGORIAS!$B$6:$L$6</definedName>
     <definedName name="CATEGORIA" localSheetId="2">[1]CATEGORIAS!$B$6:$L$6</definedName>
-    <definedName name="CATEGORIA" localSheetId="3">[1]CATEGORIAS!$B$6:$L$6</definedName>
-    <definedName name="CATEGORIA" localSheetId="5">[1]CATEGORIAS!$B$6:$L$6</definedName>
-    <definedName name="CATEGORIA" localSheetId="1">[1]CATEGORIAS!$B$6:$L$6</definedName>
     <definedName name="CATEGORIA">[2]CATEGORIAS!$B$6:$L$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -67,7 +67,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="G53" authorId="0" shapeId="0" xr:uid="{28F75A77-567E-4EB7-A59E-9AC2480944CA}">
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{B10790FA-3AC8-490B-B749-585DB9CB49DD}">
       <text>
         <r>
           <rPr>
@@ -89,33 +89,6 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{B10790FA-3AC8-490B-B749-585DB9CB49DD}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="12"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>======
-ID#AAAAk5TAb30
-Vicente Cueva R    (2023-02-14 04:39:17)
-Anterior Victoria77</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>SOPORTESAP</author>
@@ -171,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="522">
   <si>
     <t xml:space="preserve"> F5FMD RQGD7 22JHJ CNWMQ</t>
   </si>
@@ -429,9 +402,6 @@
   </si>
   <si>
     <t>CURV630707QS9</t>
-  </si>
-  <si>
-    <t>http://www.sat.gob.mx/Paginas/Inicio.aspx</t>
   </si>
   <si>
     <t>SAT</t>
@@ -1598,6 +1568,156 @@
   </si>
   <si>
     <t>HAMACHI</t>
+  </si>
+  <si>
+    <t>Se realizo en la Parroquia del Sagrado Nombre de Jesus.</t>
+  </si>
+  <si>
+    <t>Fechas para relacion con Archivo de Fotografias</t>
+  </si>
+  <si>
+    <t>Alños</t>
+  </si>
+  <si>
+    <t>Fallecimiento: Vicente Cueva Toscano.</t>
+  </si>
+  <si>
+    <t>Boda: Vicente Cueva Toscano y Eloisa Ramirez Peña.</t>
+  </si>
+  <si>
+    <t>En San Martin a las 11 hrs, Pbro. Jose de Jesus Jimenez. (Eloisa Hernandez).</t>
+  </si>
+  <si>
+    <t>Nacimiento: de Vicente Cueva Ramirez</t>
+  </si>
+  <si>
+    <t>Hospital Fray Antonio Alcalde a las 20:30 hrs.</t>
+  </si>
+  <si>
+    <t>Nacimiento: Eloisa Ramirez Peña.</t>
+  </si>
+  <si>
+    <t>Defuncion: Eloisa Ramirez Peña.</t>
+  </si>
+  <si>
+    <t>Hospital Justo Sierrea a las 9:20 pm</t>
+  </si>
+  <si>
+    <t>Matrimonio: Vicente Cueva Ramirez y Maria Yolanda Sanchez Santillan.</t>
+  </si>
+  <si>
+    <t>Registro 9, Isidro Alferez Espinosa.</t>
+  </si>
+  <si>
+    <t>Nacimiento: Maria Yolanda Sanchez Santillan.</t>
+  </si>
+  <si>
+    <t>Primera Comunion: Ana Eloisa Cueva Ramirez.</t>
+  </si>
+  <si>
+    <t>Boda: Vicente Cueva Ramirez y Maria Yolanda Sanchez Santillan.</t>
+  </si>
+  <si>
+    <t>Nacimiento: Jose Emanuel Cueva Sanchez.</t>
+  </si>
+  <si>
+    <t>https://www.sat.gob.mx/portal/public/home</t>
+  </si>
+  <si>
+    <t>BIENESTAR</t>
+  </si>
+  <si>
+    <t>Banco del Bienestar</t>
+  </si>
+  <si>
+    <t>Tarjeta 5261 9601 7736 7842</t>
+  </si>
+  <si>
+    <t>Mauricio63</t>
+  </si>
+  <si>
+    <t>NIP 4243 CLABE: 16 6320 0221 6332 2010</t>
+  </si>
+  <si>
+    <t>Centro Medico A LAS 5:30 PM</t>
+  </si>
+  <si>
+    <t>Hospital Fray Antonio Alcalde A LAS 7:00 AM.</t>
+  </si>
+  <si>
+    <t>Defuncion: Irma Rebeca Cueva Ramirez,</t>
+  </si>
+  <si>
+    <t>ISSSTE Zapopan a las 9:04 am</t>
+  </si>
+  <si>
+    <t>Titulo de Propiedad Funerl Colonias (Gayosso)</t>
+  </si>
+  <si>
+    <t>E-V-18 (Calle San Jose)</t>
+  </si>
+  <si>
+    <t>A titulo de Sr. Vicente Cueva Toscano.</t>
+  </si>
+  <si>
+    <t>Sepultura: Sra. Olivia Cueva Toscano.</t>
+  </si>
+  <si>
+    <t>No. 1325C</t>
+  </si>
+  <si>
+    <t>No. 2344HC</t>
+  </si>
+  <si>
+    <t>Sepultura: Sr. Vicente Cueva Alvarez.</t>
+  </si>
+  <si>
+    <t>Sepultura: Rosa Maria Cueva Toscano.</t>
+  </si>
+  <si>
+    <t>No. 3103HC</t>
+  </si>
+  <si>
+    <t>GAVETA 1 (47 años).</t>
+  </si>
+  <si>
+    <t>GAVETA 2 (82 años)</t>
+  </si>
+  <si>
+    <t>GAVETA 3 (60 años)</t>
+  </si>
+  <si>
+    <t>Sepultura: Vicente Cueva Tocano.</t>
+  </si>
+  <si>
+    <t>No. U-0142</t>
+  </si>
+  <si>
+    <t>GAVETA 4 (57 años)</t>
+  </si>
+  <si>
+    <t>Sepultura: Teresa Toscano Vda. De Cueva.</t>
+  </si>
+  <si>
+    <t>No. 337/93</t>
+  </si>
+  <si>
+    <t>GAVETA 5 (90 años)</t>
+  </si>
+  <si>
+    <t>Primera Comunion: Yolanda Isabel Cueva Ramirez.</t>
+  </si>
+  <si>
+    <t>Templo Capilla de Jesus a las 12:00 hrs Madrina: Angelica Solorio de Reyes.</t>
+  </si>
+  <si>
+    <t>Primera Comunion: Irma Rebeca Cueva Ramirez.</t>
+  </si>
+  <si>
+    <t>Templo Capilla de Jesus a las 19:00 hrs Madrina: Ma. Emma Toscano de Ordorica.</t>
+  </si>
+  <si>
+    <t>GOOGLE</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1930,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1999,16 +2119,27 @@
     <xf numFmtId="166" fontId="18" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2041,9 +2172,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
+      <xdr:colOff>428625</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="990600" cy="981075"/>
     <xdr:pic>
@@ -2065,7 +2196,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1876425" y="85725"/>
+          <a:off x="714375" y="171450"/>
           <a:ext cx="990600" cy="981075"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2080,6 +2211,49 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="990600" cy="981075"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F2E4C80-C931-48A0-BC71-C54319197943}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1133475" y="85725"/>
+          <a:ext cx="990600" cy="981075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2122,7 +2296,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2138,49 +2312,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C25BB99D-F487-4BEE-A55B-A7C6D24D3E4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1133475" y="85725"/>
-          <a:ext cx="990600" cy="981075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>885825</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="990600" cy="981075"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image2.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F2E4C80-C931-48A0-BC71-C54319197943}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2441,6 +2572,7 @@
       <sheetName val="VACACIONES"/>
       <sheetName val="VIVIENDA"/>
       <sheetName val="TERTIUS"/>
+      <sheetName val="V2 Chente 2025"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -2549,12 +2681,19 @@
       </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5">
+        <row r="4">
+          <cell r="J4">
+            <v>21374.18</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
+      <sheetData sheetId="11" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2860,3510 +2999,1017 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}">
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.21875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
+    <col min="2" max="3" width="11.21875" style="69" customWidth="1"/>
+    <col min="4" max="4" width="47.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" customWidth="1"/>
+    <col min="6" max="6" width="51.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="72" t="s">
+        <v>473</v>
+      </c>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="69">
-        <f>MAX(B6:B427)</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="B4" s="73">
+        <v>45999</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
       <c r="D5" s="3"/>
       <c r="E5" s="5"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="29" t="s">
+      <c r="B6" s="67" t="s">
         <v>160</v>
       </c>
+      <c r="C6" s="67" t="s">
+        <v>474</v>
+      </c>
       <c r="D6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
+      <c r="B7" s="68">
+        <v>14232</v>
+      </c>
+      <c r="C7" s="70">
+        <f t="shared" ref="C7:C25" si="0">YEARFRAC($B$4,B7)</f>
+        <v>86.972222222222229</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>480</v>
+      </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+      <c r="B8" s="68">
+        <v>22887</v>
+      </c>
+      <c r="C8" s="70">
+        <f t="shared" si="0"/>
+        <v>63.274999999999999</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>476</v>
+      </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F8" s="13" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="68">
+        <v>23178</v>
+      </c>
+      <c r="C9" s="70">
+        <f t="shared" si="0"/>
+        <v>62.477777777777774</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>485</v>
+      </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F9" s="13" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="68">
+        <v>23199</v>
+      </c>
+      <c r="C10" s="70">
+        <f t="shared" si="0"/>
+        <v>62.419444444444444</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>478</v>
+      </c>
       <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F10" s="13" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="68">
+        <v>27554</v>
+      </c>
+      <c r="C11" s="70">
+        <f t="shared" si="0"/>
+        <v>50.49722222222222</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="68">
+        <v>28364</v>
+      </c>
+      <c r="C12" s="70">
+        <f t="shared" si="0"/>
+        <v>48.280555555555559</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>517</v>
+      </c>
       <c r="E12" s="10"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F12" s="13" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="68">
+        <v>28987</v>
+      </c>
+      <c r="C13" s="70">
+        <f t="shared" si="0"/>
+        <v>46.572222222222223</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="68">
+        <v>29119</v>
+      </c>
+      <c r="C14" s="70">
+        <f t="shared" si="0"/>
+        <v>46.213888888888889</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>519</v>
+      </c>
       <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F14" s="13" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="68">
+        <v>31577</v>
+      </c>
+      <c r="C15" s="70">
+        <f t="shared" si="0"/>
+        <v>39.483333333333334</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>486</v>
+      </c>
       <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F15" s="13" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="68">
+        <v>32172</v>
+      </c>
+      <c r="C16" s="70">
+        <f t="shared" si="0"/>
+        <v>37.855555555555554</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>483</v>
+      </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F16" s="13" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="68">
+        <v>32390</v>
+      </c>
+      <c r="C17" s="70">
+        <f t="shared" si="0"/>
+        <v>37.261111111111113</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="B18" s="68">
+        <v>32401</v>
+      </c>
+      <c r="C18" s="70">
+        <f t="shared" si="0"/>
+        <v>37.230555555555554</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>487</v>
+      </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="68">
+        <v>32653</v>
+      </c>
+      <c r="C19" s="70">
+        <f t="shared" si="0"/>
+        <v>36.536111111111111</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="68">
+        <v>32710</v>
+      </c>
+      <c r="C20" s="70">
+        <f t="shared" si="0"/>
+        <v>36.380555555555553</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>488</v>
+      </c>
       <c r="E20" s="10"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F20" s="13" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
+      <c r="B21" s="68">
+        <v>33096</v>
+      </c>
+      <c r="C21" s="70">
+        <f t="shared" si="0"/>
+        <v>35.325000000000003</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>475</v>
+      </c>
       <c r="E21" s="10"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="68">
+        <v>33097</v>
+      </c>
+      <c r="C22" s="70">
+        <f t="shared" si="0"/>
+        <v>35.322222222222223</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="68">
+        <v>34121</v>
+      </c>
+      <c r="C23" s="70">
+        <f t="shared" si="0"/>
+        <v>32.519444444444446</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
+      <c r="B24" s="68">
+        <v>41039</v>
+      </c>
+      <c r="C24" s="70">
+        <f t="shared" si="0"/>
+        <v>13.577777777777778</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>481</v>
+      </c>
       <c r="E24" s="10"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F24" s="13" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
+      <c r="B25" s="68">
+        <v>45950</v>
+      </c>
+      <c r="C25" s="70">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>497</v>
+      </c>
       <c r="E25" s="10"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F25" s="13" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="70"/>
       <c r="D26" s="9"/>
       <c r="E26" s="10"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="70"/>
       <c r="D27" s="9"/>
       <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F27" s="13"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="70"/>
       <c r="D28" s="9"/>
       <c r="E28" s="10"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="13"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="70"/>
       <c r="D29" s="9"/>
       <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="13"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="70"/>
       <c r="D30" s="9"/>
       <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="13"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="70"/>
       <c r="D31" s="9"/>
       <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="13"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="70"/>
       <c r="D32" s="9"/>
       <c r="E32" s="10"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="13"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="70"/>
       <c r="D33" s="9"/>
       <c r="E33" s="10"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
+      <c r="B34" s="68"/>
+      <c r="C34" s="70"/>
       <c r="D34" s="9"/>
       <c r="E34" s="10"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="13"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="70"/>
       <c r="D35" s="9"/>
       <c r="E35" s="10"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="13"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
+      <c r="B36" s="68"/>
+      <c r="C36" s="70"/>
       <c r="D36" s="9"/>
       <c r="E36" s="10"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="13"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
+      <c r="B37" s="68"/>
+      <c r="C37" s="70"/>
       <c r="D37" s="9"/>
       <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="13"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="9"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="70"/>
       <c r="D38" s="9"/>
       <c r="E38" s="10"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="9"/>
+      <c r="B39" s="68"/>
+      <c r="C39" s="70"/>
       <c r="D39" s="9"/>
       <c r="E39" s="10"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="70"/>
       <c r="D40" s="9"/>
       <c r="E40" s="10"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
+      <c r="B41" s="68"/>
+      <c r="C41" s="70"/>
       <c r="D41" s="9"/>
       <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="13"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
+      <c r="B42" s="68"/>
+      <c r="C42" s="70"/>
       <c r="D42" s="9"/>
       <c r="E42" s="10"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="13"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F42" s="13"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="9"/>
+      <c r="B43" s="68"/>
+      <c r="C43" s="70"/>
       <c r="D43" s="9"/>
       <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="13"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="9"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="70"/>
       <c r="D44" s="9"/>
       <c r="E44" s="10"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="13"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="70"/>
       <c r="D45" s="9"/>
       <c r="E45" s="10"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="13"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="8"/>
-      <c r="C46" s="9"/>
+      <c r="F45" s="13"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B46" s="68"/>
+      <c r="C46" s="70"/>
       <c r="D46" s="9"/>
       <c r="E46" s="10"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="8"/>
-      <c r="C47" s="9"/>
+      <c r="F46" s="13"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="68"/>
+      <c r="C47" s="70"/>
       <c r="D47" s="9"/>
       <c r="E47" s="10"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="8"/>
-      <c r="C48" s="9"/>
+      <c r="F47" s="13"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" s="68"/>
+      <c r="C48" s="70"/>
       <c r="D48" s="9"/>
       <c r="E48" s="10"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
+      <c r="F48" s="13"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B49" s="68"/>
+      <c r="C49" s="70"/>
       <c r="D49" s="9"/>
       <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
+      <c r="F49" s="13"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B50" s="68"/>
+      <c r="C50" s="70"/>
       <c r="D50" s="9"/>
       <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
+      <c r="F50" s="13"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B51" s="68"/>
+      <c r="C51" s="70"/>
       <c r="D51" s="9"/>
       <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
+      <c r="F51" s="13"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B52" s="68"/>
+      <c r="C52" s="70"/>
       <c r="D52" s="9"/>
       <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B53" s="68"/>
+      <c r="C53" s="70"/>
       <c r="D53" s="9"/>
       <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
+      <c r="F53" s="13"/>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B54" s="68"/>
+      <c r="C54" s="70"/>
       <c r="D54" s="9"/>
       <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
+      <c r="F54" s="13"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B55" s="68"/>
+      <c r="C55" s="70"/>
       <c r="D55" s="9"/>
       <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
+      <c r="F55" s="13"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B56" s="68"/>
+      <c r="C56" s="70"/>
       <c r="D56" s="9"/>
       <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
+      <c r="F56" s="13"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="68"/>
+      <c r="C57" s="70"/>
       <c r="D57" s="9"/>
       <c r="E57" s="10"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
+      <c r="F57" s="13"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="68"/>
+      <c r="C58" s="70"/>
       <c r="D58" s="9"/>
       <c r="E58" s="10"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="13"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="8"/>
-      <c r="C59" s="9"/>
+      <c r="F58" s="13"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="68"/>
+      <c r="C59" s="70"/>
       <c r="D59" s="9"/>
       <c r="E59" s="10"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="13"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="8"/>
-      <c r="C60" s="9"/>
+      <c r="F59" s="13"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="68"/>
+      <c r="C60" s="70"/>
       <c r="D60" s="9"/>
       <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="13"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B61" s="8"/>
-      <c r="C61" s="9"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="68"/>
+      <c r="C61" s="70"/>
       <c r="D61" s="9"/>
       <c r="E61" s="10"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="13"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
+      <c r="F61" s="13"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B62" s="68"/>
+      <c r="C62" s="70"/>
       <c r="D62" s="9"/>
       <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="12"/>
-      <c r="H62" s="13"/>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B63" s="8"/>
-      <c r="C63" s="9"/>
+      <c r="F62" s="13"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B63" s="68"/>
+      <c r="C63" s="70"/>
       <c r="D63" s="9"/>
       <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="12"/>
-      <c r="H63" s="13"/>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B64" s="8"/>
-      <c r="C64" s="9"/>
+      <c r="F63" s="13"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B64" s="68"/>
+      <c r="C64" s="70"/>
       <c r="D64" s="9"/>
       <c r="E64" s="10"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="12"/>
-      <c r="H64" s="13"/>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B65" s="8"/>
-      <c r="C65" s="9"/>
+      <c r="F64" s="13"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B65" s="68"/>
+      <c r="C65" s="70"/>
       <c r="D65" s="9"/>
       <c r="E65" s="10"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="13"/>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B66" s="8"/>
-      <c r="C66" s="9"/>
+      <c r="F65" s="13"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B66" s="68"/>
+      <c r="C66" s="70"/>
       <c r="D66" s="9"/>
       <c r="E66" s="10"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="12"/>
-      <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B67" s="8"/>
-      <c r="C67" s="9"/>
+      <c r="F66" s="13"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B67" s="68"/>
+      <c r="C67" s="70"/>
       <c r="D67" s="9"/>
       <c r="E67" s="10"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="12"/>
-      <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B68" s="8"/>
-      <c r="C68" s="9"/>
+      <c r="F67" s="13"/>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B68" s="68"/>
+      <c r="C68" s="70"/>
       <c r="D68" s="9"/>
       <c r="E68" s="10"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="12"/>
-      <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B69" s="8"/>
-      <c r="C69" s="9"/>
+      <c r="F68" s="13"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B69" s="68"/>
+      <c r="C69" s="70"/>
       <c r="D69" s="9"/>
       <c r="E69" s="10"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="13"/>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B70" s="8"/>
-      <c r="C70" s="9"/>
+      <c r="F69" s="13"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B70" s="68"/>
+      <c r="C70" s="70"/>
       <c r="D70" s="9"/>
       <c r="E70" s="10"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="13"/>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B71" s="8"/>
-      <c r="C71" s="9"/>
+      <c r="F70" s="13"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B71" s="68"/>
+      <c r="C71" s="70"/>
       <c r="D71" s="9"/>
       <c r="E71" s="10"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="12"/>
-      <c r="H71" s="13"/>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B72" s="8"/>
-      <c r="C72" s="9"/>
+      <c r="F71" s="13"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B72" s="68"/>
+      <c r="C72" s="70"/>
       <c r="D72" s="9"/>
       <c r="E72" s="10"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="12"/>
-      <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B73" s="8"/>
-      <c r="C73" s="9"/>
+      <c r="F72" s="13"/>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B73" s="68"/>
+      <c r="C73" s="70"/>
       <c r="D73" s="9"/>
       <c r="E73" s="10"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="12"/>
-      <c r="H73" s="13"/>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B74" s="8"/>
-      <c r="C74" s="9"/>
+      <c r="F73" s="13"/>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="68"/>
+      <c r="C74" s="70"/>
       <c r="D74" s="9"/>
       <c r="E74" s="10"/>
-      <c r="F74" s="11"/>
-      <c r="G74" s="12"/>
-      <c r="H74" s="13"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B75" s="8"/>
-      <c r="C75" s="9"/>
+      <c r="F74" s="13"/>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B75" s="68"/>
+      <c r="C75" s="70"/>
       <c r="D75" s="9"/>
       <c r="E75" s="10"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="13"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B76" s="8"/>
-      <c r="C76" s="9"/>
+      <c r="F75" s="13"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B76" s="68"/>
+      <c r="C76" s="70"/>
       <c r="D76" s="9"/>
       <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="13"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B77" s="8"/>
-      <c r="C77" s="9"/>
+      <c r="F76" s="13"/>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="68"/>
+      <c r="C77" s="70"/>
       <c r="D77" s="9"/>
       <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="12"/>
-      <c r="H77" s="13"/>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B78" s="8"/>
-      <c r="C78" s="9"/>
+      <c r="F77" s="13"/>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B78" s="68"/>
+      <c r="C78" s="70"/>
       <c r="D78" s="9"/>
       <c r="E78" s="10"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="13"/>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B79" s="8"/>
-      <c r="C79" s="9"/>
+      <c r="F78" s="13"/>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B79" s="68"/>
+      <c r="C79" s="70"/>
       <c r="D79" s="9"/>
       <c r="E79" s="10"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="13"/>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B80" s="8"/>
-      <c r="C80" s="9"/>
+      <c r="F79" s="13"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B80" s="68"/>
+      <c r="C80" s="70"/>
       <c r="D80" s="9"/>
       <c r="E80" s="10"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="12"/>
-      <c r="H80" s="13"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B81" s="8"/>
-      <c r="C81" s="9"/>
+      <c r="F80" s="13"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B81" s="68"/>
+      <c r="C81" s="70"/>
       <c r="D81" s="9"/>
       <c r="E81" s="10"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="12"/>
-      <c r="H81" s="13"/>
-    </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B82" s="8"/>
-      <c r="C82" s="9"/>
+      <c r="F81" s="13"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B82" s="68"/>
+      <c r="C82" s="70"/>
       <c r="D82" s="9"/>
       <c r="E82" s="10"/>
-      <c r="F82" s="11"/>
-      <c r="G82" s="12"/>
-      <c r="H82" s="13"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B83" s="8"/>
-      <c r="C83" s="9"/>
+      <c r="F82" s="13"/>
+    </row>
+    <row r="83" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B83" s="68"/>
+      <c r="C83" s="70"/>
       <c r="D83" s="9"/>
       <c r="E83" s="10"/>
-      <c r="F83" s="11"/>
-      <c r="G83" s="12"/>
-      <c r="H83" s="13"/>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B84" s="8"/>
-      <c r="C84" s="9"/>
+      <c r="F83" s="13"/>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B84" s="68"/>
+      <c r="C84" s="70"/>
       <c r="D84" s="9"/>
       <c r="E84" s="10"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="12"/>
-      <c r="H84" s="13"/>
-    </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B85" s="8"/>
-      <c r="C85" s="9"/>
+      <c r="F84" s="13"/>
+    </row>
+    <row r="85" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B85" s="68"/>
+      <c r="C85" s="70"/>
       <c r="D85" s="9"/>
       <c r="E85" s="10"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="12"/>
-      <c r="H85" s="13"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B86" s="8"/>
-      <c r="C86" s="9"/>
+      <c r="F85" s="13"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B86" s="68"/>
+      <c r="C86" s="70"/>
       <c r="D86" s="9"/>
       <c r="E86" s="10"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="13"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B87" s="8"/>
-      <c r="C87" s="9"/>
+      <c r="F86" s="13"/>
+    </row>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B87" s="68"/>
+      <c r="C87" s="70"/>
       <c r="D87" s="9"/>
       <c r="E87" s="10"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="12"/>
-      <c r="H87" s="13"/>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B88" s="8"/>
-      <c r="C88" s="9"/>
+      <c r="F87" s="13"/>
+    </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B88" s="68"/>
+      <c r="C88" s="70"/>
       <c r="D88" s="9"/>
       <c r="E88" s="10"/>
-      <c r="F88" s="11"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="13"/>
-    </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B89" s="8"/>
-      <c r="C89" s="9"/>
+      <c r="F88" s="13"/>
+    </row>
+    <row r="89" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B89" s="68"/>
+      <c r="C89" s="70"/>
       <c r="D89" s="9"/>
       <c r="E89" s="10"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="12"/>
-      <c r="H89" s="13"/>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B90" s="8"/>
-      <c r="C90" s="9"/>
+      <c r="F89" s="13"/>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B90" s="68"/>
+      <c r="C90" s="70"/>
       <c r="D90" s="9"/>
       <c r="E90" s="10"/>
-      <c r="F90" s="11"/>
-      <c r="G90" s="12"/>
-      <c r="H90" s="13"/>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B91" s="8"/>
-      <c r="C91" s="9"/>
+      <c r="F90" s="13"/>
+    </row>
+    <row r="91" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B91" s="68"/>
+      <c r="C91" s="70"/>
       <c r="D91" s="9"/>
       <c r="E91" s="10"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="13"/>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B92" s="8"/>
-      <c r="C92" s="9"/>
+      <c r="F91" s="13"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B92" s="68"/>
+      <c r="C92" s="70"/>
       <c r="D92" s="9"/>
       <c r="E92" s="10"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="12"/>
-      <c r="H92" s="13"/>
-    </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B93" s="8"/>
-      <c r="C93" s="9"/>
+      <c r="F92" s="13"/>
+    </row>
+    <row r="93" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B93" s="68"/>
+      <c r="C93" s="70"/>
       <c r="D93" s="9"/>
       <c r="E93" s="10"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="13"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B94" s="8"/>
-      <c r="C94" s="9"/>
+      <c r="F93" s="13"/>
+    </row>
+    <row r="94" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B94" s="68"/>
+      <c r="C94" s="70"/>
       <c r="D94" s="9"/>
       <c r="E94" s="10"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="12"/>
-      <c r="H94" s="13"/>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B95" s="8"/>
-      <c r="C95" s="9"/>
+      <c r="F94" s="13"/>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B95" s="68"/>
+      <c r="C95" s="70"/>
       <c r="D95" s="9"/>
       <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="13"/>
-    </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B96" s="8"/>
-      <c r="C96" s="9"/>
+      <c r="F95" s="13"/>
+    </row>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B96" s="68"/>
+      <c r="C96" s="70"/>
       <c r="D96" s="9"/>
       <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="13"/>
-    </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B97" s="8"/>
-      <c r="C97" s="9"/>
+      <c r="F96" s="13"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B97" s="68"/>
+      <c r="C97" s="70"/>
       <c r="D97" s="9"/>
       <c r="E97" s="10"/>
-      <c r="F97" s="11"/>
-      <c r="G97" s="12"/>
-      <c r="H97" s="13"/>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B98" s="8"/>
-      <c r="C98" s="9"/>
+      <c r="F97" s="13"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B98" s="68"/>
+      <c r="C98" s="70"/>
       <c r="D98" s="9"/>
       <c r="E98" s="10"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="12"/>
-      <c r="H98" s="13"/>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B99" s="8"/>
-      <c r="C99" s="9"/>
+      <c r="F98" s="13"/>
+    </row>
+    <row r="99" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B99" s="68"/>
+      <c r="C99" s="70"/>
       <c r="D99" s="9"/>
       <c r="E99" s="10"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="13"/>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B100" s="8"/>
-      <c r="C100" s="9"/>
+      <c r="F99" s="13"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B100" s="68"/>
+      <c r="C100" s="70"/>
       <c r="D100" s="9"/>
       <c r="E100" s="10"/>
-      <c r="F100" s="11"/>
-      <c r="G100" s="12"/>
-      <c r="H100" s="13"/>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B101" s="8"/>
-      <c r="C101" s="9"/>
+      <c r="F100" s="13"/>
+    </row>
+    <row r="101" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B101" s="68"/>
+      <c r="C101" s="70"/>
       <c r="D101" s="9"/>
       <c r="E101" s="10"/>
-      <c r="F101" s="11"/>
-      <c r="G101" s="12"/>
-      <c r="H101" s="13"/>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B102" s="8"/>
-      <c r="C102" s="9"/>
+      <c r="F101" s="13"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B102" s="68"/>
+      <c r="C102" s="70"/>
       <c r="D102" s="9"/>
       <c r="E102" s="10"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="12"/>
-      <c r="H102" s="13"/>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B103" s="8"/>
-      <c r="C103" s="9"/>
+      <c r="F102" s="13"/>
+    </row>
+    <row r="103" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B103" s="68"/>
+      <c r="C103" s="70"/>
       <c r="D103" s="9"/>
       <c r="E103" s="10"/>
-      <c r="F103" s="11"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="13"/>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B104" s="8"/>
-      <c r="C104" s="9"/>
+      <c r="F103" s="13"/>
+    </row>
+    <row r="104" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B104" s="68"/>
+      <c r="C104" s="70"/>
       <c r="D104" s="9"/>
       <c r="E104" s="10"/>
-      <c r="F104" s="11"/>
-      <c r="G104" s="12"/>
-      <c r="H104" s="13"/>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B105" s="8"/>
-      <c r="C105" s="9"/>
+      <c r="F104" s="13"/>
+    </row>
+    <row r="105" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B105" s="68"/>
+      <c r="C105" s="70"/>
       <c r="D105" s="9"/>
       <c r="E105" s="10"/>
-      <c r="F105" s="11"/>
-      <c r="G105" s="12"/>
-      <c r="H105" s="13"/>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B106" s="8"/>
-      <c r="C106" s="9"/>
+      <c r="F105" s="13"/>
+    </row>
+    <row r="106" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B106" s="68"/>
+      <c r="C106" s="70"/>
       <c r="D106" s="9"/>
       <c r="E106" s="10"/>
-      <c r="F106" s="11"/>
-      <c r="G106" s="12"/>
-      <c r="H106" s="13"/>
+      <c r="F106" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="B6:H106" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H96">
-    <sortCondition ref="C7:C96"/>
-    <sortCondition ref="D7:D96"/>
+  <autoFilter ref="B6:F106" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F25">
+    <sortCondition ref="B7:B25"/>
   </sortState>
   <mergeCells count="3">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61C9082-AC22-49B6-949D-38C15B9951F8}">
-  <sheetPr>
-    <tabColor rgb="FFFF0066"/>
-  </sheetPr>
-  <dimension ref="A1:I58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.21875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-    </row>
-    <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="69">
-        <f>MAX(B6:B347)</f>
-        <v>45968</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="8">
-        <v>45435</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="8">
-        <v>45033</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B9" s="8">
-        <v>45434</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B10" s="8">
-        <v>45768</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="13" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B11" s="8">
-        <v>45768</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="8">
-        <v>45509</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="8">
-        <v>45828</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>383</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.2">
-      <c r="B14" s="8">
-        <v>45831</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="H14" s="43" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B15" s="8">
-        <v>45828</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>390</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="8">
-        <v>45508</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="8">
-        <v>45666</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="8">
-        <v>45666</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="8">
-        <v>45790</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="8">
-        <v>45889</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="11" t="s">
-        <v>439</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="8">
-        <v>44606</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B22" s="8">
-        <v>45505</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23" s="8">
-        <v>45043</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24" s="8">
-        <v>45043</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B25" s="8">
-        <v>45043</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="8">
-        <v>45664</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="8">
-        <v>44661</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="H27" s="13"/>
-    </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="8">
-        <v>43613</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="8">
-        <v>43665</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="8">
-        <v>45755</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="8">
-        <v>45035</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="8">
-        <v>45540</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="8">
-        <v>45726</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="8">
-        <v>45726</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="8">
-        <v>45554</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="8">
-        <v>45827</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>380</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="8">
-        <v>45887</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="44">
-        <v>45545</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="46" t="s">
-        <v>340</v>
-      </c>
-      <c r="F38" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="H38" s="49" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="8">
-        <v>45866</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>423</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="13" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="8">
-        <v>45835</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>400</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="8">
-        <v>45835</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="8">
-        <v>45835</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="8">
-        <v>45880</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="8">
-        <v>45854</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>412</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="8">
-        <v>45854</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="H45" s="13" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="8">
-        <v>45862</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="8">
-        <v>45880</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="F47" s="11"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="13" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="8">
-        <v>45968</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="F48" s="11"/>
-      <c r="G48" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="13"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H38">
-    <sortCondition ref="D7:D38"/>
-    <sortCondition ref="E7:E38"/>
-  </sortState>
-  <mergeCells count="3">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="H7" r:id="rId1" xr:uid="{2B9393DA-1406-4AF5-9FF3-4B1125176216}"/>
-    <hyperlink ref="F22" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
-    <hyperlink ref="E30" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
-    <hyperlink ref="E10" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
-    <hyperlink ref="F11" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
-    <hyperlink ref="G45" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
-    <hyperlink ref="G46" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
-    <hyperlink ref="E39" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
-    <hyperlink ref="F43" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
-    <hyperlink ref="E31" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId11"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B501E8-22E3-49FD-8B10-41FFB851A25C}">
-  <sheetPr>
-    <tabColor rgb="FFFF0066"/>
-  </sheetPr>
-  <dimension ref="A1:H60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="3.33203125" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.21875" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-    </row>
-    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="69">
-        <f>MAX(B6:B381)</f>
-        <v>45770</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="8">
-        <v>45604</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="8">
-        <v>45604</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="8">
-        <v>45574</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="8">
-        <v>45541</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="8">
-        <v>45757</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="8">
-        <v>45188</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="8">
-        <v>45757</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="8">
-        <v>45140</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="8">
-        <v>45609</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="8">
-        <v>45609</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="8">
-        <v>45567</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="8">
-        <v>45721</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" s="8">
-        <v>45450</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="8">
-        <v>45450</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="B21" s="8">
-        <v>45196</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="8">
-        <v>45357</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="H22" s="13"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="8">
-        <v>45715</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="8">
-        <v>45715</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>289</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="8">
-        <v>45722</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F26" s="11">
-        <v>777</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="8">
-        <v>45541</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>256</v>
-      </c>
-      <c r="F27" s="11">
-        <v>777</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
-      <c r="B28" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F28" s="11">
-        <v>777</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="8">
-        <v>45532</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F29" s="11">
-        <v>777</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="8">
-        <v>44927</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F30" s="11"/>
-      <c r="G30" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="H30" s="13"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="F31" s="11">
-        <v>777</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="8">
-        <v>45532</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="F32" s="11">
-        <v>777</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="8">
-        <v>44965</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="8">
-        <v>44927</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="8">
-        <v>45400</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="8">
-        <v>45770</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="8">
-        <v>45342</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="2"/>
-      <c r="B38" s="8">
-        <v>45342</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="2"/>
-      <c r="B39" s="8">
-        <v>44927</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="13" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="13" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="13" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="8">
-        <v>44927</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="8">
-        <v>44927</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="H45" s="13"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="8">
-        <v>45000</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="H47" s="13"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="8">
-        <v>44993</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="8">
-        <v>45604</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="G49" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="8">
-        <v>45604</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="8">
-        <v>44565</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="G51" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="8">
-        <v>45609</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="H52" s="13"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="8">
-        <v>45753</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="8">
-        <v>45753</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="8">
-        <v>45753</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="G55" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B57" s="8"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="12"/>
-      <c r="H58" s="13"/>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B59" s="8"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="11"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="13"/>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B60" s="8"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="12"/>
-      <c r="H60" s="13"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="B6:H60" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <mergeCells count="3">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1" xr:uid="{6DAF68C4-ECAD-4CC2-8448-7D43F7496622}"/>
-    <hyperlink ref="E13" r:id="rId2" xr:uid="{861633A6-0E3C-4369-809B-94928B267597}"/>
-    <hyperlink ref="F36" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
-    <hyperlink ref="E53" r:id="rId4" xr:uid="{2471DC2A-56AC-4F1A-A757-5E6A56562DA8}"/>
-    <hyperlink ref="E54" r:id="rId5" xr:uid="{8ECCA7BD-F22F-48FD-B64C-A98463D42905}"/>
-    <hyperlink ref="F53" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
-    <hyperlink ref="F54" r:id="rId7" xr:uid="{5917506B-1068-4DA5-89AA-F27F037AE325}"/>
-    <hyperlink ref="E55" r:id="rId8" xr:uid="{24389F56-00DD-47EA-A8DC-02A43544EB26}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId9"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75747C45-B5BA-4D54-921D-87E49D767A20}">
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
@@ -6393,40 +4039,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="B3" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="69">
+      <c r="B4" s="73">
         <f>MAX(B6:B389)</f>
         <v>45880</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -6441,25 +4087,25 @@
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6470,19 +4116,19 @@
         <v>37</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -6496,16 +4142,16 @@
         <v>31</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>84</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -6519,13 +4165,13 @@
         <v>55</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H9" s="19">
         <v>475869</v>
@@ -6542,16 +4188,16 @@
         <v>55</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -6585,19 +4231,19 @@
         <v>37</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G12" s="18" t="s">
         <v>34</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -6611,10 +4257,10 @@
         <v>51</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>23</v>
@@ -6629,19 +4275,19 @@
         <v>37</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -6652,10 +4298,10 @@
         <v>37</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F15" s="24" t="s">
         <v>22</v>
@@ -6673,10 +4319,10 @@
         <v>37</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>22</v>
@@ -6694,16 +4340,16 @@
         <v>37</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H17" s="26" t="s">
         <v>22</v>
@@ -6717,19 +4363,19 @@
         <v>37</v>
       </c>
       <c r="D18" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="F18" s="11" t="s">
         <v>299</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>300</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -6743,10 +4389,10 @@
         <v>47</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>34</v>
@@ -6764,16 +4410,16 @@
         <v>47</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G20" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -6784,7 +4430,7 @@
         <v>37</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E21" s="10">
         <v>-23</v>
@@ -6801,10 +4447,10 @@
         <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>22</v>
@@ -6813,7 +4459,7 @@
         <v>34</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -6824,19 +4470,19 @@
         <v>37</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -6847,19 +4493,19 @@
         <v>37</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -6870,19 +4516,19 @@
         <v>37</v>
       </c>
       <c r="D25" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E25" s="30" t="s">
         <v>364</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>365</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -6893,19 +4539,19 @@
         <v>37</v>
       </c>
       <c r="D26" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="E26" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>117</v>
-      </c>
       <c r="H26" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -6916,19 +4562,19 @@
         <v>37</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H27" s="36" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -6939,19 +4585,19 @@
         <v>37</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G28" s="14" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -6962,19 +4608,19 @@
         <v>37</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -6985,19 +4631,19 @@
         <v>37</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -7008,19 +4654,19 @@
         <v>37</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G31" s="18" t="s">
         <v>34</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -7031,13 +4677,13 @@
         <v>37</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>409</v>
-      </c>
       <c r="F32" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>84</v>
@@ -7052,17 +4698,17 @@
         <v>37</v>
       </c>
       <c r="D33" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>22</v>
       </c>
       <c r="G33" s="12"/>
       <c r="H33" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -7073,19 +4719,19 @@
         <v>37</v>
       </c>
       <c r="D34" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="36" t="s">
         <v>99</v>
-      </c>
-      <c r="E34" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G34" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="H34" s="36" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -7096,10 +4742,10 @@
         <v>37</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>22</v>
@@ -7108,7 +4754,7 @@
         <v>34</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -7119,17 +4765,17 @@
         <v>37</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -7140,19 +4786,19 @@
         <v>37</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -7163,13 +4809,13 @@
         <v>37</v>
       </c>
       <c r="D38" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E38" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="F38" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="G38" s="18" t="s">
         <v>49</v>
@@ -7186,10 +4832,10 @@
         <v>37</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>86</v>
+        <v>489</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>85</v>
@@ -7198,7 +4844,7 @@
         <v>84</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -7308,7 +4954,7 @@
         <v>66</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H44" s="13"/>
     </row>
@@ -7385,16 +5031,16 @@
         <v>37</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E48" s="30" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>22</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H48" s="13"/>
     </row>
@@ -7429,16 +5075,16 @@
         <v>37</v>
       </c>
       <c r="D50" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E50" s="26" t="s">
         <v>432</v>
-      </c>
-      <c r="E50" s="26" t="s">
-        <v>433</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>22</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H50" s="13"/>
     </row>
@@ -7450,19 +5096,19 @@
         <v>37</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F51" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="H51" s="13" t="s">
         <v>435</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -7652,22 +5298,2470 @@
     <hyperlink ref="F35" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
     <hyperlink ref="E15" r:id="rId21" xr:uid="{24B9D316-C43F-4E45-A3FC-348F1BC5501D}"/>
     <hyperlink ref="F15" r:id="rId22" xr:uid="{CBCE9FA7-4504-4520-B59C-D974CE2099B7}"/>
-    <hyperlink ref="E38" r:id="rId23" xr:uid="{A83B458E-37FA-49B6-BB18-91C4B602ED10}"/>
-    <hyperlink ref="E44" r:id="rId24" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
-    <hyperlink ref="F27" r:id="rId25" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
-    <hyperlink ref="F11" r:id="rId26" xr:uid="{16FC9D2A-4AC9-4E47-9F68-1F6F2F32790A}"/>
-    <hyperlink ref="H18" r:id="rId27" display="vcuevar@gmail.com" xr:uid="{2BC56FD7-7E2B-4127-AFB2-59B9E06C1F4A}"/>
-    <hyperlink ref="F28" r:id="rId28" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
-    <hyperlink ref="E25" r:id="rId29" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
-    <hyperlink ref="F29" r:id="rId30" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
-    <hyperlink ref="F32" r:id="rId31" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
-    <hyperlink ref="E48" r:id="rId32" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
-    <hyperlink ref="H43" r:id="rId33" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
+    <hyperlink ref="E44" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
+    <hyperlink ref="F27" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
+    <hyperlink ref="F11" r:id="rId25" xr:uid="{16FC9D2A-4AC9-4E47-9F68-1F6F2F32790A}"/>
+    <hyperlink ref="H18" r:id="rId26" display="vcuevar@gmail.com" xr:uid="{2BC56FD7-7E2B-4127-AFB2-59B9E06C1F4A}"/>
+    <hyperlink ref="F28" r:id="rId27" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
+    <hyperlink ref="E25" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
+    <hyperlink ref="F29" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
+    <hyperlink ref="F32" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
+    <hyperlink ref="E48" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
+    <hyperlink ref="H43" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId34"/>
-  <drawing r:id="rId35"/>
-  <legacyDrawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId33"/>
+  <drawing r:id="rId34"/>
+  <legacyDrawing r:id="rId35"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61C9082-AC22-49B6-949D-38C15B9951F8}">
+  <sheetPr>
+    <tabColor rgb="FFFF0066"/>
+  </sheetPr>
+  <dimension ref="A1:I58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.21875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="73">
+        <f>MAX(B6:B347)</f>
+        <v>45968</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B7" s="8">
+        <v>45435</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B8" s="8">
+        <v>45033</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B9" s="8">
+        <v>45434</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B10" s="8">
+        <v>45768</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B11" s="8">
+        <v>45768</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B12" s="8">
+        <v>45509</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B13" s="8">
+        <v>45828</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+      <c r="B14" s="8">
+        <v>45831</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H14" s="43" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B15" s="8">
+        <v>45828</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="8">
+        <v>45508</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="8">
+        <v>45666</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="8">
+        <v>45666</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="8">
+        <v>45790</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="8">
+        <v>45889</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="8">
+        <v>44606</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="8">
+        <v>45505</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="8">
+        <v>45043</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1059</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="8">
+        <v>45043</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="11">
+        <v>1059</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25" s="8">
+        <v>45043</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26" s="8">
+        <v>45664</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="8">
+        <v>44661</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="13"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B28" s="8">
+        <v>43613</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B29" s="8">
+        <v>43665</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="8">
+        <v>45755</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B31" s="8">
+        <v>45035</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E31" s="30" t="s">
+        <v>307</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32" s="8">
+        <v>45540</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="8">
+        <v>45726</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="8">
+        <v>45726</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="8">
+        <v>45554</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="8">
+        <v>45827</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="8">
+        <v>45887</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="44">
+        <v>45545</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="F38" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H38" s="49" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="8">
+        <v>45866</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="8">
+        <v>45835</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41" s="8">
+        <v>45835</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="8">
+        <v>45835</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="8">
+        <v>45880</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="8">
+        <v>45854</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="8">
+        <v>45854</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="8">
+        <v>45862</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="8">
+        <v>45880</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="F47" s="11"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="13" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="8">
+        <v>45968</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="F48" s="11"/>
+      <c r="G48" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="8"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="13"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="8"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="13"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="8"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="13"/>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="8"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="13"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B53" s="8"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="13"/>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="8"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="13"/>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B55" s="8"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="13"/>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B56" s="8"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B57" s="8"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B58" s="8"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H38">
+    <sortCondition ref="D7:D38"/>
+    <sortCondition ref="E7:E38"/>
+  </sortState>
+  <mergeCells count="3">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{2B9393DA-1406-4AF5-9FF3-4B1125176216}"/>
+    <hyperlink ref="F22" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
+    <hyperlink ref="E30" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
+    <hyperlink ref="E10" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
+    <hyperlink ref="F11" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
+    <hyperlink ref="G45" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
+    <hyperlink ref="G46" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
+    <hyperlink ref="E39" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
+    <hyperlink ref="F43" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
+    <hyperlink ref="E31" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId11"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88B501E8-22E3-49FD-8B10-41FFB851A25C}">
+  <sheetPr>
+    <tabColor rgb="FFFF0066"/>
+  </sheetPr>
+  <dimension ref="A1:H60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.21875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="73">
+        <f>MAX(B6:B381)</f>
+        <v>45770</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+    </row>
+    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="8">
+        <v>45604</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="8">
+        <v>45604</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="8">
+        <v>45574</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="8">
+        <v>45541</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="8">
+        <v>45757</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="8">
+        <v>45188</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="8">
+        <v>45757</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="8">
+        <v>45140</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="8">
+        <v>45609</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="8">
+        <v>45609</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
+      <c r="B17" s="8">
+        <v>45567</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="8">
+        <v>45721</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="13" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
+      <c r="B19" s="8">
+        <v>45450</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
+      <c r="B20" s="8">
+        <v>45450</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="8">
+        <v>45196</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="8">
+        <v>45357</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="8">
+        <v>45715</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="8">
+        <v>45715</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="8">
+        <v>45722</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F26" s="11">
+        <v>777</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="8">
+        <v>45541</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F27" s="11">
+        <v>777</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="11">
+        <v>777</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="8">
+        <v>45532</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F29" s="11">
+        <v>777</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
+      <c r="B30" s="8">
+        <v>44927</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F30" s="11"/>
+      <c r="G30" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="H30" s="13"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F31" s="11">
+        <v>777</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="8">
+        <v>45532</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="F32" s="11">
+        <v>777</v>
+      </c>
+      <c r="G32" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="8">
+        <v>44965</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="8">
+        <v>44927</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="8">
+        <v>45400</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="8">
+        <v>45770</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="8">
+        <v>45342</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="8">
+        <v>45342</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="8">
+        <v>44927</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" s="11"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="13" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F42" s="11"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="13" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="8">
+        <v>44927</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="8">
+        <v>44927</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>219</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="13"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="8">
+        <v>45000</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="8">
+        <v>44993</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="H48" s="13"/>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="8">
+        <v>45604</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H49" s="13"/>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="8">
+        <v>45604</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="13"/>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="8">
+        <v>44565</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="8">
+        <v>45609</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="H52" s="13"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B53" s="8">
+        <v>45753</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="G53" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B54" s="8">
+        <v>45753</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="G54" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B55" s="8">
+        <v>45753</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B56" s="8"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B57" s="8"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B58" s="8"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="13"/>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B59" s="8"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="13"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B60" s="8"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B6:H60" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E18" r:id="rId1" xr:uid="{6DAF68C4-ECAD-4CC2-8448-7D43F7496622}"/>
+    <hyperlink ref="E13" r:id="rId2" xr:uid="{861633A6-0E3C-4369-809B-94928B267597}"/>
+    <hyperlink ref="F36" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
+    <hyperlink ref="E53" r:id="rId4" xr:uid="{2471DC2A-56AC-4F1A-A757-5E6A56562DA8}"/>
+    <hyperlink ref="E54" r:id="rId5" xr:uid="{8ECCA7BD-F22F-48FD-B64C-A98463D42905}"/>
+    <hyperlink ref="F53" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
+    <hyperlink ref="F54" r:id="rId7" xr:uid="{5917506B-1068-4DA5-89AA-F27F037AE325}"/>
+    <hyperlink ref="E55" r:id="rId8" xr:uid="{24389F56-00DD-47EA-A8DC-02A43544EB26}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -7697,38 +7791,38 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="B3" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="69">
+      <c r="B4" s="73">
         <f>MAX(B6:B389)</f>
         <v>45965</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="50"/>
@@ -7744,32 +7838,32 @@
         <v>45965</v>
       </c>
       <c r="C7" s="60" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D7" s="61"/>
       <c r="E7" s="62"/>
       <c r="F7" s="56" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G7" s="53">
         <v>7.5</v>
       </c>
       <c r="H7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C8" s="63" t="s">
+        <v>463</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>462</v>
+      </c>
+      <c r="E8" s="64" t="s">
         <v>464</v>
       </c>
-      <c r="D8" s="63" t="s">
-        <v>463</v>
-      </c>
-      <c r="E8" s="64" t="s">
+      <c r="F8" s="65" t="s">
         <v>465</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>466</v>
       </c>
       <c r="G8" s="63"/>
     </row>
@@ -7778,10 +7872,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="E9" t="s">
         <v>457</v>
-      </c>
-      <c r="E9" t="s">
-        <v>458</v>
       </c>
       <c r="F9" s="56">
         <f>C9/$C$13</f>
@@ -7797,10 +7891,10 @@
         <v>7</v>
       </c>
       <c r="D10" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="E10" t="s">
         <v>459</v>
-      </c>
-      <c r="E10" t="s">
-        <v>460</v>
       </c>
       <c r="F10" s="56">
         <f t="shared" ref="F10:F12" si="0">C10/$C$13</f>
@@ -7816,10 +7910,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F11" s="56">
         <f t="shared" si="0"/>
@@ -7835,10 +7929,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E12" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F12" s="56">
         <f t="shared" si="0"/>
@@ -7907,40 +8001,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="71" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="B3" s="72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="69">
+      <c r="B4" s="73">
         <f>MAX(B6:B340)</f>
-        <v>45934</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+        <v>46035</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -7955,25 +8049,25 @@
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -7987,7 +8081,7 @@
         <v>55</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>54</v>
@@ -8010,16 +8104,16 @@
         <v>55</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>447</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>396</v>
-      </c>
       <c r="H8" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -8033,13 +8127,13 @@
         <v>51</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>48</v>
@@ -8097,10 +8191,10 @@
         <v>43</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>448</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>449</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="12"/>
@@ -8114,10 +8208,10 @@
         <v>43</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>450</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>451</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
@@ -8131,40 +8225,74 @@
         <v>43</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>452</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>453</v>
       </c>
       <c r="F14" s="11"/>
       <c r="G14" s="12"/>
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="13"/>
+      <c r="B15" s="8">
+        <v>46011</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
+      <c r="B16" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>521</v>
+      </c>
       <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="12"/>
+      <c r="F16" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>493</v>
+      </c>
       <c r="H16" s="13"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="8">
+        <v>46035</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>105</v>
+      </c>
       <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
+      <c r="F17" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>493</v>
+      </c>
       <c r="H17" s="13"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -8195,9 +8323,11 @@
   <hyperlinks>
     <hyperlink ref="F11" r:id="rId1" xr:uid="{A103A37A-BAD9-4367-A173-2D832BE36244}"/>
     <hyperlink ref="E9" r:id="rId2" xr:uid="{2FA7A0CC-9FFC-40BA-9FE4-1D063542C612}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{1C32F3A7-3408-4EC9-A02E-E314B31CB55A}"/>
+    <hyperlink ref="F17" r:id="rId4" xr:uid="{2BF0F368-DFC1-44BE-B71E-6D082AD4DAAA}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="88" orientation="landscape" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup scale="88" orientation="landscape" r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
--- a/PARA EL RETIRO/ACCESOS VARIOS.xlsx
+++ b/PARA EL RETIRO/ACCESOS VARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/PARA EL RETIRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1092" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA08F124-61B3-42AB-88AD-1B813EA39703}"/>
+  <xr:revisionPtr revIDLastSave="1093" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069B3EE1-E2CE-4E74-9BE9-7FC85A287318}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
   </bookViews>
   <sheets>
     <sheet name="FECHAS" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="524">
   <si>
     <t xml:space="preserve"> F5FMD RQGD7 22JHJ CNWMQ</t>
   </si>
@@ -1636,9 +1636,6 @@
     <t>Mauricio63</t>
   </si>
   <si>
-    <t>NIP 4243 CLABE: 16 6320 0221 6332 2010</t>
-  </si>
-  <si>
     <t>Centro Medico A LAS 5:30 PM</t>
   </si>
   <si>
@@ -1718,6 +1715,15 @@
   </si>
   <si>
     <t>GOOGLE</t>
+  </si>
+  <si>
+    <t>AT &amp; T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APLICACIÓN </t>
+  </si>
+  <si>
+    <t>NIP 1509 CLABE: 16 6320 0221 6332 2010</t>
   </si>
 </sst>
 </file>
@@ -2704,9 +2710,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2744,7 +2750,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2850,7 +2856,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2992,7 +2998,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3123,7 +3129,7 @@
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3153,13 +3159,13 @@
         <v>50.49722222222222</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="13" t="s">
         <v>500</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3172,11 +3178,11 @@
         <v>48.280555555555559</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -3189,13 +3195,13 @@
         <v>46.572222222222223</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>503</v>
-      </c>
       <c r="F13" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -3208,11 +3214,11 @@
         <v>46.213888888888889</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -3259,13 +3265,13 @@
         <v>37.261111111111113</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -3293,13 +3299,13 @@
         <v>36.536111111111111</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>507</v>
-      </c>
       <c r="F19" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -3316,7 +3322,7 @@
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -3344,13 +3350,13 @@
         <v>35.322222222222223</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="13" t="s">
         <v>512</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -3363,13 +3369,13 @@
         <v>32.519444444444446</v>
       </c>
       <c r="D23" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="F23" s="13" t="s">
         <v>515</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -3399,11 +3405,11 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -4424,70 +4430,68 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
-        <v>45497</v>
-      </c>
-      <c r="C21" s="9" t="s">
+        <v>45880</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="E21" s="10">
-        <v>-23</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
+        <v>431</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>112</v>
+      </c>
       <c r="H21" s="13"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="8">
-        <v>44564</v>
+        <v>45497</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H22" s="27" t="s">
-        <v>121</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E22" s="10">
+        <v>-23</v>
+      </c>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="8">
-        <v>44215</v>
+        <v>44564</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>278</v>
+        <v>123</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>279</v>
+        <v>34</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="8">
-        <v>44958</v>
+        <v>44215</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>37</v>
@@ -4495,68 +4499,68 @@
       <c r="D24" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="9" t="s">
-        <v>119</v>
+      <c r="E24" s="10" t="s">
+        <v>278</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="12" t="s">
         <v>118</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>117</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="8">
-        <v>45782</v>
+        <v>44958</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>364</v>
+        <v>120</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="14" t="s">
         <v>118</v>
       </c>
       <c r="H25" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B26" s="8">
+        <v>45782</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E26" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="13" t="s">
         <v>365</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" s="31">
-        <v>45335</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="E26" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="31">
-        <v>45663</v>
+        <v>45335</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>37</v>
@@ -4567,42 +4571,42 @@
       <c r="E27" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="F27" s="34" t="s">
+      <c r="F27" s="37" t="s">
         <v>113</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H27" s="36" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B28" s="8">
-        <v>45740</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="31">
+        <v>45663</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H28" s="13" t="s">
+      <c r="G28" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="H28" s="36" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="8">
-        <v>45828</v>
+        <v>45740</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>37</v>
@@ -4617,170 +4621,172 @@
         <v>113</v>
       </c>
       <c r="G29" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30" s="8">
+        <v>45828</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>381</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B30" s="16">
-        <v>45127</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="16">
-        <v>45014</v>
+        <v>45127</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="28" t="s">
-        <v>102</v>
+        <v>107</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32" s="8">
-        <v>45847</v>
+      <c r="B32" s="16">
+        <v>45014</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>408</v>
+        <v>105</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H32" s="13"/>
+        <v>103</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="8">
+        <v>45847</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="13"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="8">
         <v>45671</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D34" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E34" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F34" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="13" t="s">
+      <c r="G34" s="12"/>
+      <c r="H34" s="13" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34" s="40">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="40">
         <v>44620</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C35" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="D35" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="41" t="s">
+      <c r="E35" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F34" s="35" t="s">
+      <c r="F35" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="G34" s="42" t="s">
+      <c r="G35" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="H34" s="36" t="s">
+      <c r="H35" s="36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="16">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="16">
         <v>45318</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C36" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D36" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E36" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F36" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G36" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="13" t="s">
+      <c r="H36" s="13" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="8">
-        <v>44967</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="8">
-        <v>45232</v>
+        <v>44967</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>37</v>
@@ -4789,44 +4795,42 @@
         <v>92</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>90</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F37" s="14"/>
       <c r="G37" s="14" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="16">
-        <v>44851</v>
+      <c r="B38" s="8">
+        <v>45232</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>489</v>
+      <c r="D38" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>49</v>
+        <v>90</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="16">
-        <v>45846</v>
+        <v>44851</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>37</v>
@@ -4834,40 +4838,40 @@
       <c r="D39" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="27" t="s">
         <v>489</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>406</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="16">
-        <v>44930</v>
-      </c>
-      <c r="C40" s="13" t="s">
+        <v>45846</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>80</v>
+      <c r="D40" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>489</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>82</v>
+        <v>406</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -4890,77 +4894,79 @@
         <v>34</v>
       </c>
       <c r="H41" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="16">
+        <v>44930</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="13" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="8">
-        <v>45362</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="8">
-        <v>45161</v>
+        <v>45362</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="8">
+        <v>45161</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E44" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F44" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="27" t="s">
+      <c r="G44" s="14"/>
+      <c r="H44" s="27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="16">
-        <v>45488</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E44" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="H44" s="13"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="16">
-        <v>44958</v>
+        <v>45488</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>37</v>
@@ -4968,147 +4974,147 @@
       <c r="D45" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="26" t="s">
-        <v>70</v>
+      <c r="E45" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>34</v>
+        <v>362</v>
       </c>
       <c r="H45" s="13"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="16">
-        <v>45120</v>
+        <v>44958</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F46" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="13"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="16">
+        <v>45120</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="E47" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G47" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H46" s="13" t="s">
+      <c r="H47" s="13" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="8">
-        <v>45310</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="14"/>
-      <c r="H47" s="13" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="8">
+        <v>45310</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F48" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="14"/>
+      <c r="H48" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="8">
         <v>45863</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G48" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="16">
-        <v>44927</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="26" t="s">
-        <v>57</v>
+        <v>421</v>
+      </c>
+      <c r="E49" s="30" t="s">
+        <v>420</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G49" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>56</v>
-      </c>
+      <c r="G49" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="13"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" s="8">
-        <v>45880</v>
+        <v>41918</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="E50" s="26" t="s">
-        <v>432</v>
-      </c>
-      <c r="F50" s="14" t="s">
-        <v>22</v>
+        <v>437</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>433</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="13"/>
+        <v>434</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="8">
-        <v>41918</v>
+      <c r="B51" s="16">
+        <v>44927</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>433</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>434</v>
+        <v>58</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>435</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -5266,9 +5272,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B6:H68" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H49">
-    <sortCondition ref="D7:D49"/>
-    <sortCondition ref="E7:E49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H51">
+    <sortCondition ref="D7:D51"/>
+    <sortCondition ref="E7:E51"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -5279,35 +5285,35 @@
     <hyperlink ref="E12" r:id="rId1" xr:uid="{15C086F2-F597-4D51-B2E7-3FAD96221D78}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{8BB978DC-E232-48F0-9939-636AAC0E6406}"/>
     <hyperlink ref="F16" r:id="rId3" xr:uid="{92544A31-8743-4333-B41A-FC5AFE5A1056}"/>
-    <hyperlink ref="F26" r:id="rId4" xr:uid="{82D17D54-F1FB-4528-8C20-0FDDE784D3DA}"/>
+    <hyperlink ref="F27" r:id="rId4" xr:uid="{82D17D54-F1FB-4528-8C20-0FDDE784D3DA}"/>
     <hyperlink ref="E17" r:id="rId5" xr:uid="{EAA12730-E964-4FF6-8B15-29788EDF5E5A}"/>
     <hyperlink ref="H17" r:id="rId6" xr:uid="{6126EC3D-FD40-4669-A1D5-C19D1CA3EBFE}"/>
-    <hyperlink ref="E31" r:id="rId7" xr:uid="{DC0A551E-2043-4838-8B1D-E6890D4FF633}"/>
-    <hyperlink ref="H31" r:id="rId8" xr:uid="{AF14144D-3EEB-40CC-BAC6-8BA7FEAC55F2}"/>
-    <hyperlink ref="E45" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
-    <hyperlink ref="E46" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
-    <hyperlink ref="E49" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
+    <hyperlink ref="E32" r:id="rId7" xr:uid="{DC0A551E-2043-4838-8B1D-E6890D4FF633}"/>
+    <hyperlink ref="H32" r:id="rId8" xr:uid="{AF14144D-3EEB-40CC-BAC6-8BA7FEAC55F2}"/>
+    <hyperlink ref="E46" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
+    <hyperlink ref="E47" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
+    <hyperlink ref="E51" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
     <hyperlink ref="E10" r:id="rId12" xr:uid="{2A9A4DB1-04E3-4AEC-9748-2C41FBA8890F}"/>
-    <hyperlink ref="E34" r:id="rId13" xr:uid="{F7C616EB-3A49-4692-9217-779F9011DE23}"/>
-    <hyperlink ref="F34" r:id="rId14" xr:uid="{4B10E67E-EC62-43AA-877D-FB5D2D4285F6}"/>
-    <hyperlink ref="E40" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
-    <hyperlink ref="F37" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
-    <hyperlink ref="E41" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
-    <hyperlink ref="E47" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
-    <hyperlink ref="E35" r:id="rId19" xr:uid="{89E68C26-BCFC-43A5-BFA4-A8E225383626}"/>
-    <hyperlink ref="F35" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
+    <hyperlink ref="E35" r:id="rId13" xr:uid="{F7C616EB-3A49-4692-9217-779F9011DE23}"/>
+    <hyperlink ref="F35" r:id="rId14" xr:uid="{4B10E67E-EC62-43AA-877D-FB5D2D4285F6}"/>
+    <hyperlink ref="E41" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
+    <hyperlink ref="F38" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
+    <hyperlink ref="E42" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
+    <hyperlink ref="E48" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
+    <hyperlink ref="E36" r:id="rId19" xr:uid="{89E68C26-BCFC-43A5-BFA4-A8E225383626}"/>
+    <hyperlink ref="F36" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
     <hyperlink ref="E15" r:id="rId21" xr:uid="{24B9D316-C43F-4E45-A3FC-348F1BC5501D}"/>
     <hyperlink ref="F15" r:id="rId22" xr:uid="{CBCE9FA7-4504-4520-B59C-D974CE2099B7}"/>
-    <hyperlink ref="E44" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
-    <hyperlink ref="F27" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
+    <hyperlink ref="E45" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
+    <hyperlink ref="F28" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
     <hyperlink ref="F11" r:id="rId25" xr:uid="{16FC9D2A-4AC9-4E47-9F68-1F6F2F32790A}"/>
     <hyperlink ref="H18" r:id="rId26" display="vcuevar@gmail.com" xr:uid="{2BC56FD7-7E2B-4127-AFB2-59B9E06C1F4A}"/>
-    <hyperlink ref="F28" r:id="rId27" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
-    <hyperlink ref="E25" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
-    <hyperlink ref="F29" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
-    <hyperlink ref="F32" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
-    <hyperlink ref="E48" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
-    <hyperlink ref="H43" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
+    <hyperlink ref="F29" r:id="rId27" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
+    <hyperlink ref="E26" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
+    <hyperlink ref="F30" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
+    <hyperlink ref="F33" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
+    <hyperlink ref="E49" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
+    <hyperlink ref="H44" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId33"/>
@@ -5487,28 +5493,26 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="8">
-        <v>45768</v>
+        <v>45880</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>354</v>
+        <v>429</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>355</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="F10" s="11"/>
       <c r="G10" s="12"/>
       <c r="H10" s="13" t="s">
-        <v>357</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
-        <v>45768</v>
+        <v>45828</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>4</v>
@@ -5517,19 +5521,21 @@
         <v>354</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="G11" s="12"/>
+        <v>383</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>385</v>
+      </c>
       <c r="H11" s="13" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="8">
-        <v>45509</v>
+        <v>45768</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>4</v>
@@ -5538,21 +5544,19 @@
         <v>354</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>442</v>
+        <v>356</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>315</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="G12" s="12"/>
       <c r="H12" s="13" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="8">
-        <v>45828</v>
+        <v>45509</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>4</v>
@@ -5561,62 +5565,60 @@
         <v>354</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>383</v>
+        <v>314</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>384</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.2">
       <c r="B14" s="8">
-        <v>45831</v>
+        <v>45768</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>387</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="H14" s="43" t="s">
-        <v>393</v>
+        <v>359</v>
+      </c>
+      <c r="G14" s="12"/>
+      <c r="H14" s="13" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="8">
-        <v>45828</v>
+        <v>45880</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>389</v>
+        <v>425</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>314</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -5690,674 +5692,678 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="8">
-        <v>45790</v>
+        <v>45968</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>366</v>
+        <v>471</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>344</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>369</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="8">
-        <v>45889</v>
+        <v>45831</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E20" s="10"/>
+        <v>386</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>391</v>
+      </c>
       <c r="F20" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
+        <v>387</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H20" s="43" t="s">
+        <v>393</v>
+      </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
-        <v>44606</v>
+        <v>45828</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>14</v>
+        <v>386</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="8">
-        <v>45505</v>
+        <v>45790</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>14</v>
+        <v>366</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>11</v>
+        <v>367</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="G22" s="12" t="s">
+        <v>368</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>10</v>
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="8">
-        <v>45043</v>
+        <v>45889</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>15</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="8">
-        <v>45043</v>
+        <v>44606</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="11">
-        <v>1059</v>
+        <v>321</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>322</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>15</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="8">
-        <v>45043</v>
+        <v>45505</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>326</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
-        <v>45664</v>
+        <v>45043</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>346</v>
+        <v>17</v>
+      </c>
+      <c r="F26" s="11">
+        <v>1059</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>16</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>347</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="8">
-        <v>44661</v>
+        <v>45043</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>344</v>
+        <v>17</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1059</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H27" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="8">
-        <v>43613</v>
+        <v>45043</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>327</v>
+        <v>18</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>331</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="8">
-        <v>43665</v>
+        <v>45835</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>327</v>
+        <v>5</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>328</v>
+        <v>403</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>329</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>333</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="8">
-        <v>45755</v>
+        <v>45664</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>306</v>
+        <v>5</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>307</v>
+        <v>345</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>310</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
-        <v>45035</v>
+        <v>44661</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>307</v>
+        <v>5</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>310</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H31" s="13"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="8">
-        <v>45540</v>
+        <v>43613</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="8">
-        <v>45726</v>
+        <v>43665</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>192</v>
+        <v>332</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="8">
-        <v>45726</v>
+        <v>45755</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>192</v>
+        <v>309</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="8">
-        <v>45554</v>
+        <v>45035</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>8</v>
+        <v>306</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>307</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>6</v>
+        <v>308</v>
+      </c>
+      <c r="G35" s="12" t="s">
+        <v>309</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>5</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="8">
-        <v>45827</v>
+        <v>45540</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>377</v>
+        <v>335</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>379</v>
+        <v>336</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="8">
-        <v>45887</v>
+        <v>45726</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>9</v>
+        <v>300</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>440</v>
+        <v>303</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>7</v>
+        <v>301</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>441</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38" s="44">
-        <v>45545</v>
-      </c>
-      <c r="C38" s="45" t="s">
+      <c r="B38" s="8">
+        <v>45726</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F38" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="H38" s="49" t="s">
-        <v>439</v>
+      <c r="D38" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="8">
-        <v>45866</v>
+        <v>45827</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>379</v>
+      </c>
       <c r="H39" s="13" t="s">
-        <v>423</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="8">
-        <v>45835</v>
+        <v>45866</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G40" s="12" t="s">
-        <v>399</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="F40" s="11"/>
+      <c r="G40" s="12"/>
       <c r="H40" s="13" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
-        <v>45835</v>
+        <v>45854</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>6</v>
+        <v>411</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="8">
-        <v>45835</v>
+        <v>45862</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>5</v>
+        <v>409</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>329</v>
+        <v>417</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>346</v>
+        <v>418</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="8">
-        <v>45880</v>
+        <v>45854</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>314</v>
+        <v>412</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>413</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>23</v>
+        <v>414</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="8">
-        <v>45854</v>
+        <v>45835</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>398</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="8">
-        <v>45854</v>
+        <v>45554</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>409</v>
+        <v>9</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>412</v>
+        <v>8</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>414</v>
+        <v>7</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>6</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>415</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="8">
-        <v>45862</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="B46" s="44">
+        <v>45545</v>
+      </c>
+      <c r="C46" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="H46" s="13" t="s">
-        <v>415</v>
+      <c r="D46" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>339</v>
+      </c>
+      <c r="F46" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H46" s="49" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="8">
-        <v>45880</v>
+        <v>45887</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>429</v>
+        <v>9</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="F47" s="11"/>
-      <c r="G47" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>6</v>
+      </c>
       <c r="H47" s="13" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="8">
-        <v>45968</v>
+        <v>45835</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>471</v>
+        <v>400</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F48" s="11"/>
+        <v>401</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>402</v>
+      </c>
       <c r="G48" s="12" t="s">
-        <v>470</v>
+        <v>6</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>468</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -6452,9 +6458,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H38">
-    <sortCondition ref="D7:D38"/>
-    <sortCondition ref="E7:E38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H48">
+    <sortCondition ref="D7:D48"/>
+    <sortCondition ref="E7:E48"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -6463,15 +6469,15 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{2B9393DA-1406-4AF5-9FF3-4B1125176216}"/>
-    <hyperlink ref="F22" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
-    <hyperlink ref="E30" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
-    <hyperlink ref="E10" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
-    <hyperlink ref="F11" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
-    <hyperlink ref="G45" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
-    <hyperlink ref="G46" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
-    <hyperlink ref="E39" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
-    <hyperlink ref="F43" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
-    <hyperlink ref="E31" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
+    <hyperlink ref="F25" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
+    <hyperlink ref="E34" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
+    <hyperlink ref="E12" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
+    <hyperlink ref="F14" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
+    <hyperlink ref="G43" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
+    <hyperlink ref="G42" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
+    <hyperlink ref="E40" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
+    <hyperlink ref="F15" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
+    <hyperlink ref="E35" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId11"/>
@@ -6838,21 +6844,25 @@
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="8">
-        <v>45721</v>
+        <v>45450</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>296</v>
-      </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+        <v>180</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>181</v>
+      </c>
       <c r="H18" s="13" t="s">
-        <v>295</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -6866,242 +6876,238 @@
       <c r="D19" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>24</v>
-      </c>
+      <c r="E19" s="10"/>
       <c r="F19" s="11" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="8">
-        <v>45450</v>
+        <v>45196</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E20" s="10"/>
+        <v>186</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>187</v>
+      </c>
       <c r="F20" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>184</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G20" s="12"/>
       <c r="H20" s="13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="8">
-        <v>45196</v>
+        <v>45721</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>188</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="E21" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="8">
-        <v>45357</v>
+        <v>45753</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>253</v>
+        <v>372</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>169</v>
+        <v>375</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="13"/>
+        <v>454</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="8">
-        <v>45715</v>
+        <v>45753</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>284</v>
+        <v>373</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>375</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>288</v>
+        <v>454</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>285</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="8">
-        <v>45715</v>
+        <v>45753</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>286</v>
+        <v>372</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>287</v>
+        <v>200</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>285</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="8">
-        <v>45722</v>
+        <v>45357</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>290</v>
+        <v>243</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>291</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>293</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="8">
-        <v>44993</v>
+        <v>45715</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F26" s="11">
-        <v>777</v>
+        <v>283</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>284</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="8">
-        <v>45541</v>
+        <v>45715</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>255</v>
-      </c>
-      <c r="F27" s="11">
-        <v>777</v>
+        <v>286</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>287</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="8">
-        <v>44993</v>
+        <v>45722</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>256</v>
+        <v>290</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="F28" s="11">
-        <v>777</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>192</v>
+        <v>289</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>292</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="8">
-        <v>45532</v>
+        <v>44993</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="F29" s="11">
         <v>777</v>
@@ -7110,28 +7116,32 @@
         <v>192</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="8">
-        <v>44927</v>
+        <v>45541</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>261</v>
-      </c>
-      <c r="F30" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="F30" s="11">
+        <v>777</v>
+      </c>
       <c r="G30" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="H30" s="13"/>
+        <v>192</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
@@ -7142,10 +7152,10 @@
         <v>32</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="F31" s="11">
         <v>777</v>
@@ -7154,7 +7164,7 @@
         <v>192</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7166,10 +7176,10 @@
         <v>32</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="F32" s="11">
         <v>777</v>
@@ -7178,109 +7188,105 @@
         <v>192</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="8">
-        <v>44965</v>
+        <v>44927</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>274</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="F33" s="11"/>
       <c r="G33" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>276</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="H33" s="13"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="8">
-        <v>44927</v>
+        <v>44993</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>196</v>
+        <v>264</v>
+      </c>
+      <c r="F34" s="11">
+        <v>777</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="8">
-        <v>45400</v>
+        <v>45532</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>200</v>
+        <v>266</v>
+      </c>
+      <c r="F35" s="11">
+        <v>777</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="8">
-        <v>45770</v>
+        <v>44965</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>194</v>
+        <v>272</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>113</v>
+        <v>274</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>361</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="8">
-        <v>45342</v>
+        <v>44927</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>32</v>
@@ -7289,22 +7295,22 @@
         <v>194</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>169</v>
+        <v>197</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="8">
-        <v>45342</v>
+        <v>45400</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>32</v>
@@ -7313,18 +7319,22 @@
         <v>194</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="12"/>
+        <v>199</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="H38" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="8">
-        <v>44927</v>
+        <v>45770</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>32</v>
@@ -7336,121 +7346,121 @@
         <v>206</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>207</v>
+        <v>361</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="8">
-        <v>44993</v>
+        <v>45342</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+        <v>202</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>169</v>
+      </c>
       <c r="H40" s="13" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="8">
-        <v>44993</v>
+        <v>45342</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="12"/>
       <c r="H41" s="13" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="8">
-        <v>44993</v>
+        <v>44927</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="12"/>
+        <v>206</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>197</v>
+      </c>
       <c r="H42" s="13" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="8">
-        <v>44927</v>
+        <v>44993</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>271</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="F43" s="11"/>
+      <c r="G43" s="12"/>
       <c r="H43" s="13" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="8">
-        <v>44927</v>
+        <v>44993</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>219</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F44" s="11"/>
+      <c r="G44" s="12"/>
       <c r="H44" s="13" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7462,64 +7472,64 @@
         <v>32</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="H45" s="13"/>
+        <v>215</v>
+      </c>
+      <c r="F45" s="11"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="13" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="8">
-        <v>45000</v>
+        <v>44927</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>7</v>
+        <v>270</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="8">
-        <v>44993</v>
+        <v>44927</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="H47" s="13"/>
+        <v>219</v>
+      </c>
+      <c r="H47" s="13" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
@@ -7530,173 +7540,169 @@
         <v>32</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H48" s="13"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="8">
-        <v>45604</v>
+        <v>45000</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>30</v>
+        <v>225</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="13"/>
+        <v>223</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" s="8">
-        <v>45604</v>
+        <v>44993</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>233</v>
+        <v>7</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>28</v>
+        <v>223</v>
       </c>
       <c r="H50" s="13"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="8">
-        <v>44565</v>
+        <v>44993</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>236</v>
+        <v>7</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>238</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" s="8">
-        <v>45609</v>
+        <v>45604</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>242</v>
+        <v>28</v>
       </c>
       <c r="H52" s="13"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="8">
-        <v>45753</v>
+        <v>45604</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>294</v>
+        <v>231</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>372</v>
+        <v>163</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>375</v>
+        <v>233</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>453</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="8">
-        <v>45753</v>
+        <v>44565</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>375</v>
+        <v>235</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>236</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>454</v>
+        <v>237</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>374</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="8">
-        <v>45753</v>
+        <v>45609</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>294</v>
+        <v>239</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>372</v>
+        <v>240</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>376</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -7745,20 +7751,23 @@
     </row>
   </sheetData>
   <autoFilter ref="B6:H60" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H55">
+    <sortCondition ref="D7:D55"/>
+  </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E18" r:id="rId1" xr:uid="{6DAF68C4-ECAD-4CC2-8448-7D43F7496622}"/>
+    <hyperlink ref="E21" r:id="rId1" xr:uid="{6DAF68C4-ECAD-4CC2-8448-7D43F7496622}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{861633A6-0E3C-4369-809B-94928B267597}"/>
-    <hyperlink ref="F36" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
-    <hyperlink ref="E53" r:id="rId4" xr:uid="{2471DC2A-56AC-4F1A-A757-5E6A56562DA8}"/>
-    <hyperlink ref="E54" r:id="rId5" xr:uid="{8ECCA7BD-F22F-48FD-B64C-A98463D42905}"/>
-    <hyperlink ref="F53" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
-    <hyperlink ref="F54" r:id="rId7" xr:uid="{5917506B-1068-4DA5-89AA-F27F037AE325}"/>
-    <hyperlink ref="E55" r:id="rId8" xr:uid="{24389F56-00DD-47EA-A8DC-02A43544EB26}"/>
+    <hyperlink ref="F39" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
+    <hyperlink ref="E22" r:id="rId4" xr:uid="{2471DC2A-56AC-4F1A-A757-5E6A56562DA8}"/>
+    <hyperlink ref="E23" r:id="rId5" xr:uid="{8ECCA7BD-F22F-48FD-B64C-A98463D42905}"/>
+    <hyperlink ref="F22" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
+    <hyperlink ref="F23" r:id="rId7" xr:uid="{5917506B-1068-4DA5-89AA-F27F037AE325}"/>
+    <hyperlink ref="E24" r:id="rId8" xr:uid="{24389F56-00DD-47EA-A8DC-02A43544EB26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId9"/>
@@ -7976,7 +7985,7 @@
     <tabColor rgb="FFFF0066"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -8072,26 +8081,24 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" s="8">
-        <v>45934</v>
+        <v>46035</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>445</v>
+        <v>521</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>522</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>52</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" s="8">
@@ -8104,16 +8111,16 @@
         <v>55</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>446</v>
+        <v>54</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>395</v>
+        <v>53</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>444</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -8124,63 +8131,65 @@
         <v>43</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>141</v>
+        <v>55</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>394</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>50</v>
+        <v>446</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>443</v>
+        <v>395</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>48</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" s="8">
-        <v>44927</v>
+        <v>46011</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>46</v>
+        <v>490</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>491</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="13"/>
+        <v>492</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
-        <v>45307</v>
+        <v>45934</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>41</v>
+        <v>51</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>39</v>
+        <v>443</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -8191,10 +8200,10 @@
         <v>43</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="12"/>
@@ -8202,60 +8211,60 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="8">
-        <v>45934</v>
+        <v>44927</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
+        <v>47</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="8">
-        <v>45934</v>
+        <v>46035</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12"/>
+        <v>520</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>493</v>
+      </c>
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="8">
-        <v>46011</v>
+        <v>45934</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>494</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
@@ -8265,7 +8274,7 @@
         <v>43</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>521</v>
+        <v>105</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="11" t="s">
@@ -8278,28 +8287,40 @@
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="8">
-        <v>46035</v>
+        <v>45307</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="10"/>
+        <v>42</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="F17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>493</v>
-      </c>
-      <c r="H17" s="13"/>
+      <c r="G17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
+      <c r="B18" s="8">
+        <v>45934</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>448</v>
+      </c>
       <c r="F18" s="11"/>
       <c r="G18" s="12"/>
       <c r="H18" s="13"/>
@@ -8313,21 +8334,70 @@
       <c r="G19" s="12"/>
       <c r="H19" s="13"/>
     </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="13"/>
+    </row>
   </sheetData>
   <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H18">
+    <sortCondition ref="D7:D18"/>
+  </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="B4:H4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F11" r:id="rId1" xr:uid="{A103A37A-BAD9-4367-A173-2D832BE36244}"/>
-    <hyperlink ref="E9" r:id="rId2" xr:uid="{2FA7A0CC-9FFC-40BA-9FE4-1D063542C612}"/>
-    <hyperlink ref="F16" r:id="rId3" xr:uid="{1C32F3A7-3408-4EC9-A02E-E314B31CB55A}"/>
-    <hyperlink ref="F17" r:id="rId4" xr:uid="{2BF0F368-DFC1-44BE-B71E-6D082AD4DAAA}"/>
+    <hyperlink ref="F17" r:id="rId1" xr:uid="{A103A37A-BAD9-4367-A173-2D832BE36244}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{2FA7A0CC-9FFC-40BA-9FE4-1D063542C612}"/>
+    <hyperlink ref="F14" r:id="rId3" xr:uid="{1C32F3A7-3408-4EC9-A02E-E314B31CB55A}"/>
+    <hyperlink ref="F16" r:id="rId4" xr:uid="{2BF0F368-DFC1-44BE-B71E-6D082AD4DAAA}"/>
+    <hyperlink ref="F7" r:id="rId5" xr:uid="{7B0A587E-E1B7-49D7-9ED4-5B1D288A46BB}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="88" orientation="landscape" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup scale="88" orientation="landscape" r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
--- a/PARA EL RETIRO/ACCESOS VARIOS.xlsx
+++ b/PARA EL RETIRO/ACCESOS VARIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/PARA EL RETIRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1093" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{069B3EE1-E2CE-4E74-9BE9-7FC85A287318}"/>
+  <xr:revisionPtr revIDLastSave="1159" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34BD663-06C3-4878-84EE-3B40476C75C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
   </bookViews>
   <sheets>
     <sheet name="FECHAS" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,9 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$106</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ITEKNIA!$B$6:$H$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VMA!$B$6:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ITEKNIA!$B$6:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VMA!$B$6:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">YOLANDA!$B$6:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$19</definedName>
     <definedName name="BANCOS" localSheetId="0">[1]CATEGORIAS!$C$8:$C$20</definedName>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="550">
   <si>
     <t xml:space="preserve"> F5FMD RQGD7 22JHJ CNWMQ</t>
   </si>
@@ -1591,9 +1591,6 @@
     <t>Nacimiento: de Vicente Cueva Ramirez</t>
   </si>
   <si>
-    <t>Hospital Fray Antonio Alcalde a las 20:30 hrs.</t>
-  </si>
-  <si>
     <t>Nacimiento: Eloisa Ramirez Peña.</t>
   </si>
   <si>
@@ -1606,9 +1603,6 @@
     <t>Matrimonio: Vicente Cueva Ramirez y Maria Yolanda Sanchez Santillan.</t>
   </si>
   <si>
-    <t>Registro 9, Isidro Alferez Espinosa.</t>
-  </si>
-  <si>
     <t>Nacimiento: Maria Yolanda Sanchez Santillan.</t>
   </si>
   <si>
@@ -1639,9 +1633,6 @@
     <t>Centro Medico A LAS 5:30 PM</t>
   </si>
   <si>
-    <t>Hospital Fray Antonio Alcalde A LAS 7:00 AM.</t>
-  </si>
-  <si>
     <t>Defuncion: Irma Rebeca Cueva Ramirez,</t>
   </si>
   <si>
@@ -1724,6 +1715,93 @@
   </si>
   <si>
     <t>NIP 1509 CLABE: 16 6320 0221 6332 2010</t>
+  </si>
+  <si>
+    <t>Recogi mi posible ultimo INE Vicente Cueva Ramirez</t>
+  </si>
+  <si>
+    <t>Vigencia del 2026 al 2036, a ver si llego a los 73 años.</t>
+  </si>
+  <si>
+    <t>SASY630616JCNNL13</t>
+  </si>
+  <si>
+    <t>IMSS DIGITAL (CELULAR)</t>
+  </si>
+  <si>
+    <t>TP-LINK</t>
+  </si>
+  <si>
+    <t>www.tp-link.com/support</t>
+  </si>
+  <si>
+    <t>Para extensores de WiFi. Aplicación Celular.</t>
+  </si>
+  <si>
+    <t>CURVvice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocar las 4 primeras letras de tu RFC en mayúscula + 4 primeros caracteres de tu cuenta de correo electrónico en minúscula </t>
+  </si>
+  <si>
+    <t>OFICILIA 10, LIBRO 84, ACTA 3910, GUADALAJARA. 13/AGOSTO/1990.</t>
+  </si>
+  <si>
+    <t>Fallecimiento: Vicente Cueva Alvarez.</t>
+  </si>
+  <si>
+    <t>OFICIALIZ 10, LIBRO 29 ACTA 3064 GUADALAJARA. 05/SEPTIEMBRE/1988</t>
+  </si>
+  <si>
+    <t>Matrimonio: Vicente Cueva Alvarez y Teresa Toscano .</t>
+  </si>
+  <si>
+    <t>Nacimiento: Ana Eloisa Ramirez Cueva</t>
+  </si>
+  <si>
+    <t>OFICINA 1 LIBRO 260 ACTA NO. 1518 A LAS 9:30 HORAS.</t>
+  </si>
+  <si>
+    <t>OFICIALIA 9, ACTA 82 LIBRO 15 GDL. Isidro Alferez Espinosa.</t>
+  </si>
+  <si>
+    <t>Nacimiento: Elvia Dolores Sanchez Santillan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/MARZ/1970, OFICINA 1, LIBRO 1775, FOJA 109, ACTA 218. (3:30 HORAS) </t>
+  </si>
+  <si>
+    <t>4/AGO/1977 OFICINA 1 LIBRO 2410 ACTA FOJA 780 NO. 15046 (12:45 HORAS)</t>
+  </si>
+  <si>
+    <t>Nacimiento: Gloria Santillan Cornejo.</t>
+  </si>
+  <si>
+    <t>Fallecimiento: Gloria Santillan Cornejo.</t>
+  </si>
+  <si>
+    <t>21/07/2015 OFICIALIA 5 LIBRO 8 ACTA 1564 GDL ( 9:30 AM)</t>
+  </si>
+  <si>
+    <t>Fallecimiento: Jose Sanchez Torres.</t>
+  </si>
+  <si>
+    <t>OFICIALIA 9, ACTA 742 LIBRO 4 (23/JUN/1981).</t>
+  </si>
+  <si>
+    <t>Nacimiento: Jose Antonio Sanchez Santillan.</t>
+  </si>
+  <si>
+    <t>OFICIALIA 1, ACTA 370, LIBRO 2 (3/MAR/1966).</t>
+  </si>
+  <si>
+    <t>OFICIALIA 1, LIBRO 1311, ACTA 10632 (26/JUL/63) Hospital Fray Antonio Alcalde A LAS 7:30 AM.</t>
+  </si>
+  <si>
+    <t>OFICIALIA 1, LIBRO 1310, ACTA 10184 (16/JUL/63) Hospital Fray Antonio Alcalde a las 20:30 hrs.</t>
+  </si>
+  <si>
+    <t>https://comeritk-odoo-dev-28221883.dev.odoo.com/</t>
   </si>
 </sst>
 </file>
@@ -2578,11 +2656,10 @@
       <sheetName val="VACACIONES"/>
       <sheetName val="VIVIENDA"/>
       <sheetName val="TERTIUS"/>
-      <sheetName val="V2 Chente 2025"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="6">
           <cell r="B6" t="str">
@@ -2685,21 +2762,14 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
-        <row r="4">
-          <cell r="J4">
-            <v>21374.18</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2710,9 +2780,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2750,7 +2820,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2856,7 +2926,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2998,7 +3068,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3009,7 +3079,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -3086,403 +3156,484 @@
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="68">
-        <v>14232</v>
+        <v>10163</v>
       </c>
       <c r="C7" s="70">
-        <f t="shared" ref="C7:C25" si="0">YEARFRAC($B$4,B7)</f>
-        <v>86.972222222222229</v>
+        <f t="shared" ref="C7:C34" si="0">YEARFRAC($B$4,B7)</f>
+        <v>98.111111111111114</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>480</v>
+        <v>533</v>
       </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="13"/>
+      <c r="F7" s="13" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="68">
-        <v>22887</v>
+        <v>13473</v>
       </c>
       <c r="C8" s="70">
         <f t="shared" si="0"/>
-        <v>63.274999999999999</v>
+        <v>89.052777777777777</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>476</v>
+        <v>540</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="13" t="s">
-        <v>477</v>
-      </c>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="68">
-        <v>23178</v>
+        <v>14232</v>
       </c>
       <c r="C9" s="70">
         <f t="shared" si="0"/>
-        <v>62.477777777777774</v>
+        <v>86.972222222222229</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="E9" s="10"/>
-      <c r="F9" s="13" t="s">
-        <v>495</v>
-      </c>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="68">
-        <v>23199</v>
+        <v>22887</v>
       </c>
       <c r="C10" s="70">
         <f t="shared" si="0"/>
-        <v>62.419444444444444</v>
+        <v>63.274999999999999</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="68">
-        <v>27554</v>
+        <v>23178</v>
       </c>
       <c r="C11" s="70">
         <f t="shared" si="0"/>
-        <v>50.49722222222222</v>
+        <v>62.477777777777774</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>499</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="E11" s="10"/>
       <c r="F11" s="13" t="s">
-        <v>500</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="68">
-        <v>28364</v>
+        <v>23199</v>
       </c>
       <c r="C12" s="70">
         <f t="shared" si="0"/>
-        <v>48.280555555555559</v>
+        <v>62.419444444444444</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>516</v>
+        <v>478</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="13" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="68">
-        <v>28987</v>
+        <v>25606</v>
       </c>
       <c r="C13" s="70">
         <f t="shared" si="0"/>
-        <v>46.572222222222223</v>
+        <v>55.836111111111109</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>502</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="E13" s="10"/>
       <c r="F13" s="13" t="s">
-        <v>507</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="68">
-        <v>29119</v>
+        <v>27554</v>
       </c>
       <c r="C14" s="70">
         <f t="shared" si="0"/>
-        <v>46.213888888888889</v>
+        <v>50.49722222222222</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="E14" s="10"/>
+        <v>495</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>496</v>
+      </c>
       <c r="F14" s="13" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="68">
-        <v>31577</v>
+        <v>28321</v>
       </c>
       <c r="C15" s="70">
         <f t="shared" si="0"/>
-        <v>39.483333333333334</v>
+        <v>48.397222222222226</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>486</v>
+        <v>534</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="13" t="s">
-        <v>472</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="68">
-        <v>32172</v>
+        <v>28364</v>
       </c>
       <c r="C16" s="70">
         <f t="shared" si="0"/>
-        <v>37.855555555555554</v>
+        <v>48.280555555555559</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>483</v>
+        <v>513</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="13" t="s">
-        <v>484</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="68">
-        <v>32390</v>
+        <v>28987</v>
       </c>
       <c r="C17" s="70">
         <f t="shared" si="0"/>
-        <v>37.261111111111113</v>
+        <v>46.572222222222223</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>504</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="68">
-        <v>32401</v>
+        <v>29119</v>
       </c>
       <c r="C18" s="70">
         <f t="shared" si="0"/>
-        <v>37.230555555555554</v>
+        <v>46.213888888888889</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>487</v>
+        <v>515</v>
       </c>
       <c r="E18" s="10"/>
-      <c r="F18" s="13"/>
+      <c r="F18" s="13" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="68">
-        <v>32653</v>
+        <v>31577</v>
       </c>
       <c r="C19" s="70">
         <f t="shared" si="0"/>
-        <v>36.536111111111111</v>
+        <v>39.483333333333334</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>506</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="E19" s="10"/>
       <c r="F19" s="13" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="68">
-        <v>32710</v>
+        <v>32172</v>
       </c>
       <c r="C20" s="70">
         <f t="shared" si="0"/>
-        <v>36.380555555555553</v>
+        <v>37.855555555555554</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="13" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="68">
-        <v>33096</v>
+        <v>32389</v>
       </c>
       <c r="C21" s="70">
         <f t="shared" si="0"/>
-        <v>35.325000000000003</v>
+        <v>37.263888888888886</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
       <c r="E21" s="10"/>
-      <c r="F21" s="13"/>
+      <c r="F21" s="13" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="68">
-        <v>33097</v>
+        <v>32390</v>
       </c>
       <c r="C22" s="70">
         <f t="shared" si="0"/>
-        <v>35.322222222222223</v>
+        <v>37.261111111111113</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="68">
-        <v>34121</v>
+        <v>32401</v>
       </c>
       <c r="C23" s="70">
         <f t="shared" si="0"/>
-        <v>32.519444444444446</v>
+        <v>37.230555555555554</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>515</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="68">
-        <v>41039</v>
+        <v>32653</v>
       </c>
       <c r="C24" s="70">
         <f t="shared" si="0"/>
-        <v>13.577777777777778</v>
+        <v>36.536111111111111</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="E24" s="10"/>
+        <v>502</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>503</v>
+      </c>
       <c r="F24" s="13" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="68">
-        <v>45950</v>
+        <v>32710</v>
       </c>
       <c r="C25" s="70">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>36.380555555555553</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="13" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="70"/>
-      <c r="D26" s="9"/>
+        <v>492</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="68">
+        <v>33096</v>
+      </c>
+      <c r="C26" s="70">
+        <f t="shared" si="0"/>
+        <v>35.325000000000003</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>475</v>
+      </c>
       <c r="E26" s="10"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="70"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="13"/>
+      <c r="F26" s="13" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="68">
+        <v>33097</v>
+      </c>
+      <c r="C27" s="70">
+        <f t="shared" si="0"/>
+        <v>35.322222222222223</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>509</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="13"/>
+      <c r="B28" s="68">
+        <v>34121</v>
+      </c>
+      <c r="C28" s="70">
+        <f t="shared" si="0"/>
+        <v>32.519444444444446</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>512</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="70"/>
-      <c r="D29" s="9"/>
+      <c r="B29" s="68">
+        <v>41039</v>
+      </c>
+      <c r="C29" s="70">
+        <f t="shared" si="0"/>
+        <v>13.577777777777778</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>480</v>
+      </c>
       <c r="E29" s="10"/>
-      <c r="F29" s="13"/>
+      <c r="F29" s="13" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="70"/>
-      <c r="D30" s="9"/>
+      <c r="B30" s="68">
+        <v>42205</v>
+      </c>
+      <c r="C30" s="70">
+        <f t="shared" si="0"/>
+        <v>10.383333333333333</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>541</v>
+      </c>
       <c r="E30" s="10"/>
-      <c r="F30" s="13"/>
+      <c r="F30" s="13" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="70"/>
-      <c r="D31" s="9"/>
+      <c r="B31" s="68">
+        <v>45950</v>
+      </c>
+      <c r="C31" s="70">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>493</v>
+      </c>
       <c r="E31" s="10"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="9"/>
+      <c r="F31" s="13" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="68">
+        <v>46037</v>
+      </c>
+      <c r="C32" s="70">
+        <f t="shared" si="0"/>
+        <v>0.10277777777777777</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>521</v>
+      </c>
       <c r="E32" s="10"/>
-      <c r="F32" s="13"/>
+      <c r="F32" s="13" t="s">
+        <v>522</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="70"/>
-      <c r="D33" s="9"/>
+      <c r="B33" s="68">
+        <v>29759</v>
+      </c>
+      <c r="C33" s="70">
+        <f t="shared" si="0"/>
+        <v>44.461111111111109</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>543</v>
+      </c>
       <c r="E33" s="10"/>
-      <c r="F33" s="13"/>
+      <c r="F33" s="13" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="70"/>
-      <c r="D34" s="9"/>
+      <c r="B34" s="68">
+        <v>24119</v>
+      </c>
+      <c r="C34" s="70">
+        <f t="shared" si="0"/>
+        <v>59.905555555555559</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>545</v>
+      </c>
       <c r="E34" s="10"/>
-      <c r="F34" s="13"/>
+      <c r="F34" s="13" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
@@ -3500,8 +3651,8 @@
       <c r="E36" s="10"/>
       <c r="F36" s="13"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
       <c r="B37" s="68"/>
       <c r="C37" s="70"/>
       <c r="D37" s="9"/>
@@ -3573,6 +3724,7 @@
       <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
       <c r="B46" s="68"/>
       <c r="C46" s="70"/>
       <c r="D46" s="9"/>
@@ -3999,10 +4151,17 @@
       <c r="E106" s="10"/>
       <c r="F106" s="13"/>
     </row>
+    <row r="107" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B107" s="68"/>
+      <c r="C107" s="70"/>
+      <c r="D107" s="9"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:F106" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F25">
-    <sortCondition ref="B7:B25"/>
+  <autoFilter ref="B6:F107" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F32">
+    <sortCondition ref="B7:B32"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
@@ -4020,7 +4179,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -4070,8 +4229,8 @@
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="73">
-        <f>MAX(B6:B389)</f>
-        <v>45880</v>
+        <f>MAX(B6:B390)</f>
+        <v>46059</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -4785,29 +4944,29 @@
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="8">
+      <c r="B37" s="31">
         <v>44967</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14" t="s">
+      <c r="F37" s="35"/>
+      <c r="G37" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="36" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="8">
-        <v>45232</v>
+        <v>46059</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>37</v>
@@ -4816,44 +4975,42 @@
         <v>92</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>90</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F38" s="14"/>
       <c r="G38" s="14" t="s">
-        <v>89</v>
+        <v>528</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>88</v>
+        <v>529</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="16">
-        <v>44851</v>
+      <c r="B39" s="8">
+        <v>45232</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D39" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>489</v>
+      <c r="D39" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>49</v>
+        <v>90</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="16">
-        <v>45846</v>
+        <v>44851</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>37</v>
@@ -4861,40 +5018,40 @@
       <c r="D40" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>489</v>
+      <c r="E40" s="27" t="s">
+        <v>487</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>406</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="16">
-        <v>44930</v>
-      </c>
-      <c r="C41" s="13" t="s">
+        <v>45846</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>80</v>
+      <c r="D41" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>487</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>82</v>
+        <v>406</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -4917,77 +5074,79 @@
         <v>34</v>
       </c>
       <c r="H42" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="16">
+        <v>44930</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43" s="8">
-        <v>45362</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F43" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="8">
-        <v>45161</v>
+        <v>45362</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="8">
+        <v>45161</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E45" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F45" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="27" t="s">
+      <c r="G45" s="14"/>
+      <c r="H45" s="27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="16">
-        <v>45488</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="H45" s="13"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="16">
-        <v>44958</v>
+        <v>45488</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>37</v>
@@ -4995,145 +5154,171 @@
       <c r="D46" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="26" t="s">
-        <v>70</v>
+      <c r="E46" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>34</v>
+        <v>362</v>
       </c>
       <c r="H46" s="13"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="16">
-        <v>45120</v>
+        <v>44958</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D47" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="13"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="16">
+        <v>45120</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="E48" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F48" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G48" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="13" t="s">
+      <c r="H48" s="13" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="8">
-        <v>45310</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="13" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="8">
-        <v>45863</v>
-      </c>
-      <c r="C49" s="13" t="s">
+        <v>45310</v>
+      </c>
+      <c r="C49" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="E49" s="30" t="s">
-        <v>420</v>
+        <v>61</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H49" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="G49" s="14"/>
+      <c r="H49" s="13" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" s="8">
-        <v>41918</v>
+        <v>45863</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>437</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>433</v>
+        <v>421</v>
+      </c>
+      <c r="E50" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="F50" s="14" t="s">
+        <v>22</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="H50" s="13" t="s">
-        <v>435</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H50" s="13"/>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="16">
-        <v>44927</v>
+      <c r="B51" s="8">
+        <v>41918</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D51" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="16">
+        <v>44927</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="E52" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F52" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G52" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H52" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="13"/>
-    </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
+      <c r="B53" s="8">
+        <v>46055</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>527</v>
+      </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="8"/>
@@ -5270,11 +5455,20 @@
       <c r="G68" s="12"/>
       <c r="H68" s="13"/>
     </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B69" s="8"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:H68" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H51">
-    <sortCondition ref="D7:D51"/>
-    <sortCondition ref="E7:E51"/>
+  <autoFilter ref="B6:H69" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H52">
+    <sortCondition ref="D7:D52"/>
+    <sortCondition ref="E7:E52"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -5290,21 +5484,21 @@
     <hyperlink ref="H17" r:id="rId6" xr:uid="{6126EC3D-FD40-4669-A1D5-C19D1CA3EBFE}"/>
     <hyperlink ref="E32" r:id="rId7" xr:uid="{DC0A551E-2043-4838-8B1D-E6890D4FF633}"/>
     <hyperlink ref="H32" r:id="rId8" xr:uid="{AF14144D-3EEB-40CC-BAC6-8BA7FEAC55F2}"/>
-    <hyperlink ref="E46" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
-    <hyperlink ref="E47" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
-    <hyperlink ref="E51" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
+    <hyperlink ref="E47" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
+    <hyperlink ref="E48" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
+    <hyperlink ref="E52" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
     <hyperlink ref="E10" r:id="rId12" xr:uid="{2A9A4DB1-04E3-4AEC-9748-2C41FBA8890F}"/>
     <hyperlink ref="E35" r:id="rId13" xr:uid="{F7C616EB-3A49-4692-9217-779F9011DE23}"/>
     <hyperlink ref="F35" r:id="rId14" xr:uid="{4B10E67E-EC62-43AA-877D-FB5D2D4285F6}"/>
-    <hyperlink ref="E41" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
-    <hyperlink ref="F38" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
-    <hyperlink ref="E42" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
-    <hyperlink ref="E48" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
+    <hyperlink ref="E42" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
+    <hyperlink ref="F39" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
+    <hyperlink ref="E43" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
+    <hyperlink ref="E49" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
     <hyperlink ref="E36" r:id="rId19" xr:uid="{89E68C26-BCFC-43A5-BFA4-A8E225383626}"/>
     <hyperlink ref="F36" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
     <hyperlink ref="E15" r:id="rId21" xr:uid="{24B9D316-C43F-4E45-A3FC-348F1BC5501D}"/>
     <hyperlink ref="F15" r:id="rId22" xr:uid="{CBCE9FA7-4504-4520-B59C-D974CE2099B7}"/>
-    <hyperlink ref="E45" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
+    <hyperlink ref="E46" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
     <hyperlink ref="F28" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
     <hyperlink ref="F11" r:id="rId25" xr:uid="{16FC9D2A-4AC9-4E47-9F68-1F6F2F32790A}"/>
     <hyperlink ref="H18" r:id="rId26" display="vcuevar@gmail.com" xr:uid="{2BC56FD7-7E2B-4127-AFB2-59B9E06C1F4A}"/>
@@ -5312,13 +5506,14 @@
     <hyperlink ref="E26" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
     <hyperlink ref="F30" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
     <hyperlink ref="F33" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
-    <hyperlink ref="E49" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
-    <hyperlink ref="H44" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
+    <hyperlink ref="E50" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
+    <hyperlink ref="H45" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
+    <hyperlink ref="E53" r:id="rId33" xr:uid="{F0164290-77DB-4F67-8C9C-2FE620F0B88B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId33"/>
-  <drawing r:id="rId34"/>
-  <legacyDrawing r:id="rId35"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId34"/>
+  <drawing r:id="rId35"/>
+  <legacyDrawing r:id="rId36"/>
 </worksheet>
 </file>
 
@@ -5577,7 +5772,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="8">
         <v>45768</v>
       </c>
@@ -5711,7 +5906,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="75" x14ac:dyDescent="0.2">
       <c r="B20" s="8">
         <v>45831</v>
       </c>
@@ -6489,7 +6684,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -6539,8 +6734,8 @@
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="73">
-        <f>MAX(B6:B381)</f>
-        <v>45770</v>
+        <f>MAX(B6:B382)</f>
+        <v>46058</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7071,8 +7266,8 @@
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="2"/>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
       <c r="B28" s="8">
         <v>45722</v>
       </c>
@@ -7095,8 +7290,8 @@
         <v>293</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
       <c r="B29" s="8">
         <v>44993</v>
       </c>
@@ -7211,8 +7406,8 @@
       </c>
       <c r="H33" s="13"/>
     </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="1"/>
       <c r="B34" s="8">
         <v>44993</v>
       </c>
@@ -7286,7 +7481,7 @@
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="8">
-        <v>44927</v>
+        <v>46058</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>32</v>
@@ -7295,22 +7490,16 @@
         <v>194</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>198</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="13"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="8">
-        <v>45400</v>
+        <v>44927</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>32</v>
@@ -7319,22 +7508,22 @@
         <v>194</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="8">
-        <v>45770</v>
+        <v>45400</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>32</v>
@@ -7343,22 +7532,22 @@
         <v>194</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>34</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
       <c r="B40" s="8">
-        <v>45342</v>
+        <v>45770</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>32</v>
@@ -7367,16 +7556,16 @@
         <v>194</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>203</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7391,18 +7580,22 @@
         <v>194</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="12"/>
+        <v>202</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>169</v>
+      </c>
       <c r="H41" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="8">
-        <v>44927</v>
+        <v>45342</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>32</v>
@@ -7411,36 +7604,36 @@
         <v>194</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F42" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>197</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F42" s="11"/>
+      <c r="G42" s="12"/>
       <c r="H42" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="8">
-        <v>44993</v>
+        <v>44927</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F43" s="11"/>
-      <c r="G43" s="12"/>
+        <v>206</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>197</v>
+      </c>
       <c r="H43" s="13" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7452,15 +7645,15 @@
         <v>32</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F44" s="11"/>
       <c r="G44" s="12"/>
       <c r="H44" s="13" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7472,39 +7665,35 @@
         <v>32</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F45" s="11"/>
       <c r="G45" s="12"/>
       <c r="H45" s="13" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="8">
-        <v>44927</v>
+        <v>44993</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>268</v>
+        <v>214</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>271</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="F46" s="11"/>
+      <c r="G46" s="12"/>
       <c r="H46" s="13" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7516,55 +7705,58 @@
         <v>32</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>162</v>
+        <v>270</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="8">
-        <v>44993</v>
+        <v>44927</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="H48" s="13"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
       <c r="B49" s="8">
-        <v>45000</v>
+        <v>44993</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>7</v>
@@ -7572,13 +7764,11 @@
       <c r="G49" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="H49" s="13" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H49" s="13"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B50" s="8">
-        <v>44993</v>
+        <v>45000</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>32</v>
@@ -7587,7 +7777,7 @@
         <v>224</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>7</v>
@@ -7595,9 +7785,11 @@
       <c r="G50" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H50" s="13" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B51" s="8">
         <v>44993</v>
       </c>
@@ -7605,41 +7797,41 @@
         <v>32</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="H51" s="13"/>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B52" s="8">
-        <v>45604</v>
+        <v>44993</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>30</v>
+        <v>229</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>28</v>
+        <v>230</v>
       </c>
       <c r="H52" s="13"/>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B53" s="8">
         <v>45604</v>
       </c>
@@ -7650,70 +7842,82 @@
         <v>231</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>163</v>
+        <v>30</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>28</v>
       </c>
       <c r="H53" s="13"/>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B54" s="8">
-        <v>44565</v>
+        <v>45604</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+      <c r="H54" s="13"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B55" s="8">
-        <v>45609</v>
+        <v>44565</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B56" s="8">
+        <v>45609</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E56" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F56" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G56" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
       <c r="H56" s="13"/>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
@@ -7722,7 +7926,7 @@
       <c r="G57" s="12"/>
       <c r="H57" s="13"/>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B58" s="8"/>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -7731,7 +7935,7 @@
       <c r="G58" s="12"/>
       <c r="H58" s="13"/>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B59" s="8"/>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
@@ -7740,7 +7944,7 @@
       <c r="G59" s="12"/>
       <c r="H59" s="13"/>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B60" s="8"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
@@ -7749,10 +7953,19 @@
       <c r="G60" s="12"/>
       <c r="H60" s="13"/>
     </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B61" s="8"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:H60" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H55">
-    <sortCondition ref="D7:D55"/>
+  <autoFilter ref="B6:H61" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H56">
+    <sortCondition ref="D7:D56"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -7762,7 +7975,7 @@
   <hyperlinks>
     <hyperlink ref="E21" r:id="rId1" xr:uid="{6DAF68C4-ECAD-4CC2-8448-7D43F7496622}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{861633A6-0E3C-4369-809B-94928B267597}"/>
-    <hyperlink ref="F39" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
+    <hyperlink ref="F40" r:id="rId3" xr:uid="{4DE531C6-99A6-4C9C-8B19-4C88B5185EC6}"/>
     <hyperlink ref="E22" r:id="rId4" xr:uid="{2471DC2A-56AC-4F1A-A757-5E6A56562DA8}"/>
     <hyperlink ref="E23" r:id="rId5" xr:uid="{8ECCA7BD-F22F-48FD-B64C-A98463D42905}"/>
     <hyperlink ref="F22" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
@@ -8036,7 +8249,7 @@
       <c r="A4" s="2"/>
       <c r="B4" s="73">
         <f>MAX(B6:B340)</f>
-        <v>46035</v>
+        <v>46040</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -8087,10 +8300,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>40</v>
@@ -8154,19 +8367,19 @@
         <v>43</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="G10" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>493</v>
-      </c>
       <c r="H10" s="13" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -8238,14 +8451,14 @@
         <v>43</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H14" s="13"/>
     </row>
@@ -8281,7 +8494,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H16" s="13"/>
     </row>
@@ -8326,13 +8539,25 @@
       <c r="H18" s="13"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
+      <c r="B19" s="8">
+        <v>46040</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>40</v>
+      </c>
       <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
+      <c r="H19" s="13" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="8"/>
@@ -8395,9 +8620,10 @@
     <hyperlink ref="F14" r:id="rId3" xr:uid="{1C32F3A7-3408-4EC9-A02E-E314B31CB55A}"/>
     <hyperlink ref="F16" r:id="rId4" xr:uid="{2BF0F368-DFC1-44BE-B71E-6D082AD4DAAA}"/>
     <hyperlink ref="F7" r:id="rId5" xr:uid="{7B0A587E-E1B7-49D7-9ED4-5B1D288A46BB}"/>
+    <hyperlink ref="F19" r:id="rId6" xr:uid="{F9DF7DA6-B3EB-4C2D-9CB6-65DEE887D77C}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="88" orientation="landscape" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup scale="88" orientation="landscape" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/PARA EL RETIRO/ACCESOS VARIOS.xlsx
+++ b/PARA EL RETIRO/ACCESOS VARIOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/PARA EL RETIRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1159" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B34BD663-06C3-4878-84EE-3B40476C75C5}"/>
+  <xr:revisionPtr revIDLastSave="1259" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4E91E61-FA86-417C-A1B6-FD11E04FF6B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
   </bookViews>
@@ -25,11 +25,11 @@
     <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ITEKNIA!$B$6:$H$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VMA!$B$6:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">YOLANDA!$B$6:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$20</definedName>
     <definedName name="BANCOS" localSheetId="0">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="3">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="1">[1]CATEGORIAS!$C$8:$C$20</definedName>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="592">
   <si>
     <t xml:space="preserve"> F5FMD RQGD7 22JHJ CNWMQ</t>
   </si>
@@ -555,9 +555,6 @@
   </si>
   <si>
     <t>CELULAR</t>
-  </si>
-  <si>
-    <t>Equipo que estoy usando para Zarkin.</t>
   </si>
   <si>
     <t>852 459 469</t>
@@ -1057,9 +1054,6 @@
   </si>
   <si>
     <t>Usuario de Costos - Diseño</t>
-  </si>
-  <si>
-    <t>http://187.189.177.39:8082/siz_sa/public/auth/login</t>
   </si>
   <si>
     <t>246</t>
@@ -1597,9 +1591,6 @@
     <t>Defuncion: Eloisa Ramirez Peña.</t>
   </si>
   <si>
-    <t>Hospital Justo Sierrea a las 9:20 pm</t>
-  </si>
-  <si>
     <t>Matrimonio: Vicente Cueva Ramirez y Maria Yolanda Sanchez Santillan.</t>
   </si>
   <si>
@@ -1630,9 +1621,6 @@
     <t>Mauricio63</t>
   </si>
   <si>
-    <t>Centro Medico A LAS 5:30 PM</t>
-  </si>
-  <si>
     <t>Defuncion: Irma Rebeca Cueva Ramirez,</t>
   </si>
   <si>
@@ -1802,6 +1790,144 @@
   </si>
   <si>
     <t>https://comeritk-odoo-dev-28221883.dev.odoo.com/</t>
+  </si>
+  <si>
+    <t>OFICIALIA 9, LIBRO 112, ACTA 2667 (05/AGO/1989) Centro Medico A LAS 5:30 PM</t>
+  </si>
+  <si>
+    <t>VICENTE CUEVA TOSCANO</t>
+  </si>
+  <si>
+    <t>Calle 21 No. 801 Sector Libertat, Guadalajara, Jalisco.</t>
+  </si>
+  <si>
+    <t>VICENTE CUEVA ALVARES</t>
+  </si>
+  <si>
+    <t>FRANCISCO CUEVA DEL CASTILLO.</t>
+  </si>
+  <si>
+    <t>ALTAGRACIA ALVARES</t>
+  </si>
+  <si>
+    <t>TERESA TOSCANO ROBLES</t>
+  </si>
+  <si>
+    <t>SEVERIANO TOSCANO</t>
+  </si>
+  <si>
+    <t>ESTIFANA ROBLES</t>
+  </si>
+  <si>
+    <t>Nacimiento: Vicente Cueva Toscano</t>
+  </si>
+  <si>
+    <t>OFICIALIA 1, LIBRO 559,  FORJA 119, ACTA 4227  (6/AGO/1933)</t>
+  </si>
+  <si>
+    <t>ELOISA RAMIREZ PEÑA</t>
+  </si>
+  <si>
+    <t>PADRE</t>
+  </si>
+  <si>
+    <t>ABUELO P</t>
+  </si>
+  <si>
+    <t>ABUELA P</t>
+  </si>
+  <si>
+    <t>MADRE</t>
+  </si>
+  <si>
+    <t>ABUELA M</t>
+  </si>
+  <si>
+    <t>ABUELO M</t>
+  </si>
+  <si>
+    <t>JOSE RAMIREZ NAVARRETE</t>
+  </si>
+  <si>
+    <t>TERESA PEÑA SALAZAR</t>
+  </si>
+  <si>
+    <t>oficialia 1, libro 28, acta 5567 Hospital Justo Sierrea a las 9:20 pm</t>
+  </si>
+  <si>
+    <t>USUARIO: MARY PARDO</t>
+  </si>
+  <si>
+    <t>SISTEMA1</t>
+  </si>
+  <si>
+    <t>MariaPard2&amp;</t>
+  </si>
+  <si>
+    <t>En espera de ver a quien se asigne.</t>
+  </si>
+  <si>
+    <t>Confirmacion: Vicente Cueva Ramirez.</t>
+  </si>
+  <si>
+    <t>En Catedral Basilica, Padrino: Pbro. Jose Luis Plascencia Montoya.</t>
+  </si>
+  <si>
+    <t>Nacimiento: Jose Sanchez Torres</t>
+  </si>
+  <si>
+    <t>http://187.189.177.39:8085/siz_sa/public/auth/login</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>DavidZarkin</t>
+  </si>
+  <si>
+    <t>Acceso a SIZ David Zarkin</t>
+  </si>
+  <si>
+    <t>Nicho C44</t>
+  </si>
+  <si>
+    <t>Se depositaron las cenizas de Rebeca Cueva R. En nicho de Divino Rostro.</t>
+  </si>
+  <si>
+    <t>Disturbios por parte de Narcos, tras la muerte del Mecho.</t>
+  </si>
+  <si>
+    <t>Nos enteremos porque fueron a llevar a Pao al tren ligero y estaba cerrado.</t>
+  </si>
+  <si>
+    <t>1 385 635 956</t>
+  </si>
+  <si>
+    <t>Equipo DELL</t>
+  </si>
+  <si>
+    <t>Maquina proporcionada por Zarkin.</t>
+  </si>
+  <si>
+    <t>Equipo personal</t>
+  </si>
+  <si>
+    <t>La cambie para instalar en el Nuevo Cel.</t>
+  </si>
+  <si>
+    <t>https://prezi.com</t>
+  </si>
+  <si>
+    <t>PREZI</t>
+  </si>
+  <si>
+    <t>Presentaciones Usuario Principal Eman.</t>
+  </si>
+  <si>
+    <t>jose.cueva@uteg.edu.mx</t>
+  </si>
+  <si>
+    <t>Manez107</t>
   </si>
 </sst>
 </file>
@@ -2014,7 +2140,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2214,16 +2340,25 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2377,6 +2512,94 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>286481</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>585</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A2C9928-2D9B-351B-E083-2E14119FBB4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15611475" y="2552700"/>
+          <a:ext cx="5239481" cy="4191585"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>657919</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>57690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A0F307-29FA-0FC5-C644-445EDECDCE79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15259050" y="6934200"/>
+          <a:ext cx="4972744" cy="3867690"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2514,6 +2737,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="CUENTA"/>
@@ -2643,6 +2867,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="DOC"/>
@@ -3079,7 +3304,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -3099,33 +3324,33 @@
     </row>
     <row r="2" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
     </row>
     <row r="3" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="72" t="s">
-        <v>473</v>
-      </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
+      <c r="B3" s="76" t="s">
+        <v>471</v>
+      </c>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
     </row>
     <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="73">
+      <c r="B4" s="77">
         <v>45999</v>
       </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -3138,19 +3363,19 @@
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3159,43 +3384,45 @@
         <v>10163</v>
       </c>
       <c r="C7" s="70">
-        <f t="shared" ref="C7:C34" si="0">YEARFRAC($B$4,B7)</f>
+        <f t="shared" ref="C7:C39" si="0">YEARFRAC($B$4,B7)</f>
         <v>98.111111111111114</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="13" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="68">
-        <v>13473</v>
+        <v>12245</v>
       </c>
       <c r="C8" s="70">
         <f t="shared" si="0"/>
-        <v>89.052777777777777</v>
+        <v>92.411111111111111</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="E8" s="10"/>
-      <c r="F8" s="13"/>
+      <c r="F8" s="13" t="s">
+        <v>556</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="68">
-        <v>14232</v>
+        <v>12485</v>
       </c>
       <c r="C9" s="70">
         <f t="shared" si="0"/>
-        <v>86.972222222222229</v>
+        <v>91.75277777777778</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>479</v>
+        <v>573</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="13"/>
@@ -3203,477 +3430,518 @@
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="68">
-        <v>22887</v>
+        <v>13473</v>
       </c>
       <c r="C10" s="70">
         <f t="shared" si="0"/>
-        <v>63.274999999999999</v>
+        <v>89.052777777777777</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>476</v>
+        <v>536</v>
       </c>
       <c r="E10" s="10"/>
-      <c r="F10" s="13" t="s">
-        <v>477</v>
-      </c>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="68">
-        <v>23178</v>
+        <v>14232</v>
       </c>
       <c r="C11" s="70">
         <f t="shared" si="0"/>
-        <v>62.477777777777774</v>
+        <v>86.972222222222229</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E11" s="10"/>
-      <c r="F11" s="13" t="s">
-        <v>547</v>
-      </c>
+      <c r="F11" s="13"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="68">
-        <v>23199</v>
+        <v>22887</v>
       </c>
       <c r="C12" s="70">
         <f t="shared" si="0"/>
-        <v>62.419444444444444</v>
+        <v>63.274999999999999</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="13" t="s">
-        <v>548</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="68">
-        <v>25606</v>
+        <v>23178</v>
       </c>
       <c r="C13" s="70">
         <f t="shared" si="0"/>
-        <v>55.836111111111109</v>
+        <v>62.477777777777774</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>537</v>
+        <v>480</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="13" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="68">
-        <v>27554</v>
+        <v>23199</v>
       </c>
       <c r="C14" s="70">
         <f t="shared" si="0"/>
-        <v>50.49722222222222</v>
+        <v>62.419444444444444</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>496</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="E14" s="10"/>
       <c r="F14" s="13" t="s">
-        <v>497</v>
+        <v>544</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="68">
-        <v>28321</v>
+        <v>24119</v>
       </c>
       <c r="C15" s="70">
         <f t="shared" si="0"/>
-        <v>48.397222222222226</v>
+        <v>59.905555555555559</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="13" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="68">
-        <v>28364</v>
+        <v>25606</v>
       </c>
       <c r="C16" s="70">
         <f t="shared" si="0"/>
-        <v>48.280555555555559</v>
+        <v>55.836111111111109</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="13" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="68">
-        <v>28987</v>
+        <v>27554</v>
       </c>
       <c r="C17" s="70">
         <f t="shared" si="0"/>
-        <v>46.572222222222223</v>
+        <v>50.49722222222222</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="68">
-        <v>29119</v>
+        <v>28321</v>
       </c>
       <c r="C18" s="70">
         <f t="shared" si="0"/>
-        <v>46.213888888888889</v>
+        <v>48.397222222222226</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="13" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="68">
-        <v>31577</v>
+        <v>28364</v>
       </c>
       <c r="C19" s="70">
         <f t="shared" si="0"/>
-        <v>39.483333333333334</v>
+        <v>48.280555555555559</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="13" t="s">
-        <v>472</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="68">
-        <v>32172</v>
+        <v>28554</v>
       </c>
       <c r="C20" s="70">
         <f t="shared" si="0"/>
-        <v>37.855555555555554</v>
+        <v>47.758333333333333</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>482</v>
+        <v>571</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="13" t="s">
-        <v>536</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="68">
-        <v>32389</v>
+        <v>28987</v>
       </c>
       <c r="C21" s="70">
         <f t="shared" si="0"/>
-        <v>37.263888888888886</v>
+        <v>46.572222222222223</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E21" s="10"/>
+        <v>494</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>495</v>
+      </c>
       <c r="F21" s="13" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="68">
-        <v>32390</v>
+        <v>29119</v>
       </c>
       <c r="C22" s="70">
         <f t="shared" si="0"/>
-        <v>37.261111111111113</v>
+        <v>46.213888888888889</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>500</v>
-      </c>
+        <v>511</v>
+      </c>
+      <c r="E22" s="10"/>
       <c r="F22" s="13" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="68">
-        <v>32401</v>
+        <v>29759</v>
       </c>
       <c r="C23" s="70">
         <f t="shared" si="0"/>
-        <v>37.230555555555554</v>
+        <v>44.461111111111109</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>485</v>
+        <v>539</v>
       </c>
       <c r="E23" s="10"/>
-      <c r="F23" s="13"/>
+      <c r="F23" s="13" t="s">
+        <v>540</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="68">
-        <v>32653</v>
+        <v>31577</v>
       </c>
       <c r="C24" s="70">
         <f t="shared" si="0"/>
-        <v>36.536111111111111</v>
+        <v>39.483333333333334</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>502</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>503</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="E24" s="10"/>
       <c r="F24" s="13" t="s">
-        <v>506</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="68">
-        <v>32710</v>
+        <v>32172</v>
       </c>
       <c r="C25" s="70">
         <f t="shared" si="0"/>
-        <v>36.380555555555553</v>
+        <v>37.855555555555554</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="13" t="s">
-        <v>492</v>
+        <v>532</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="68">
-        <v>33096</v>
+        <v>32389</v>
       </c>
       <c r="C26" s="70">
         <f t="shared" si="0"/>
-        <v>35.325000000000003</v>
+        <v>37.263888888888886</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>475</v>
+        <v>527</v>
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="68">
-        <v>33097</v>
+        <v>32390</v>
       </c>
       <c r="C27" s="70">
         <f t="shared" si="0"/>
-        <v>35.322222222222223</v>
+        <v>37.261111111111113</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="68">
-        <v>34121</v>
+        <v>32401</v>
       </c>
       <c r="C28" s="70">
         <f t="shared" si="0"/>
-        <v>32.519444444444446</v>
+        <v>37.230555555555554</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>512</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="E28" s="10"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="68">
-        <v>41039</v>
+        <v>32653</v>
       </c>
       <c r="C29" s="70">
         <f t="shared" si="0"/>
-        <v>13.577777777777778</v>
+        <v>36.536111111111111</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="E29" s="10"/>
+        <v>498</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>499</v>
+      </c>
       <c r="F29" s="13" t="s">
-        <v>481</v>
+        <v>502</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="68">
-        <v>42205</v>
+        <v>32710</v>
       </c>
       <c r="C30" s="70">
         <f t="shared" si="0"/>
-        <v>10.383333333333333</v>
+        <v>36.380555555555553</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>541</v>
+        <v>483</v>
       </c>
       <c r="E30" s="10"/>
       <c r="F30" s="13" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="68">
-        <v>45950</v>
+        <v>33096</v>
       </c>
       <c r="C31" s="70">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>35.325000000000003</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="E31" s="10"/>
       <c r="F31" s="13" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="68">
-        <v>46037</v>
+        <v>33097</v>
       </c>
       <c r="C32" s="70">
         <f t="shared" si="0"/>
-        <v>0.10277777777777777</v>
+        <v>35.322222222222223</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="E32" s="10"/>
+        <v>503</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>504</v>
+      </c>
       <c r="F32" s="13" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="68">
-        <v>29759</v>
+        <v>34121</v>
       </c>
       <c r="C33" s="70">
         <f t="shared" si="0"/>
-        <v>44.461111111111109</v>
+        <v>32.519444444444446</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="E33" s="10"/>
+        <v>506</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>507</v>
+      </c>
       <c r="F33" s="13" t="s">
-        <v>544</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="68">
-        <v>24119</v>
+        <v>41039</v>
       </c>
       <c r="C34" s="70">
         <f t="shared" si="0"/>
-        <v>59.905555555555559</v>
+        <v>13.577777777777778</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>545</v>
+        <v>478</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="13" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="70"/>
-      <c r="D35" s="9"/>
+      <c r="B35" s="68">
+        <v>42205</v>
+      </c>
+      <c r="C35" s="70">
+        <f t="shared" si="0"/>
+        <v>10.383333333333333</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>537</v>
+      </c>
       <c r="E35" s="10"/>
-      <c r="F35" s="13"/>
+      <c r="F35" s="13" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="9"/>
+      <c r="B36" s="68">
+        <v>45950</v>
+      </c>
+      <c r="C36" s="70">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>489</v>
+      </c>
       <c r="E36" s="10"/>
-      <c r="F36" s="13"/>
+      <c r="F36" s="13" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="70"/>
-      <c r="D37" s="9"/>
+      <c r="B37" s="68">
+        <v>46037</v>
+      </c>
+      <c r="C37" s="70">
+        <f t="shared" si="0"/>
+        <v>0.10277777777777777</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>517</v>
+      </c>
       <c r="E37" s="10"/>
-      <c r="F37" s="13"/>
+      <c r="F37" s="13" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="9"/>
+      <c r="B38" s="68">
+        <v>46075</v>
+      </c>
+      <c r="C38" s="70">
+        <f t="shared" si="0"/>
+        <v>0.20555555555555555</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>579</v>
+      </c>
       <c r="E38" s="10"/>
-      <c r="F38" s="13"/>
+      <c r="F38" s="13" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="70"/>
-      <c r="D39" s="9"/>
+      <c r="B39" s="68">
+        <v>46075</v>
+      </c>
+      <c r="C39" s="70">
+        <f t="shared" si="0"/>
+        <v>0.20555555555555555</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>580</v>
+      </c>
       <c r="E39" s="10"/>
-      <c r="F39" s="13"/>
+      <c r="F39" s="13" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
@@ -3717,140 +3985,201 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="70"/>
-      <c r="D45" s="9"/>
+      <c r="B45" s="68">
+        <v>12245</v>
+      </c>
+      <c r="C45" s="70">
+        <f t="shared" ref="C45" si="1">YEARFRAC($B$4,B45)</f>
+        <v>92.411111111111111</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>547</v>
+      </c>
       <c r="E45" s="10"/>
-      <c r="F45" s="13"/>
+      <c r="F45" s="13" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="68"/>
-      <c r="C46" s="70"/>
-      <c r="D46" s="9"/>
+      <c r="C46" s="70" t="s">
+        <v>558</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>549</v>
+      </c>
       <c r="E46" s="10"/>
       <c r="F46" s="13"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
       <c r="B47" s="68"/>
-      <c r="C47" s="70"/>
-      <c r="D47" s="9"/>
+      <c r="C47" s="70" t="s">
+        <v>559</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>550</v>
+      </c>
       <c r="E47" s="10"/>
       <c r="F47" s="13"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
       <c r="B48" s="68"/>
-      <c r="C48" s="70"/>
-      <c r="D48" s="9"/>
+      <c r="C48" s="70" t="s">
+        <v>560</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>551</v>
+      </c>
       <c r="E48" s="10"/>
       <c r="F48" s="13"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
       <c r="B49" s="68"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="9"/>
+      <c r="C49" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>552</v>
+      </c>
       <c r="E49" s="10"/>
       <c r="F49" s="13"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
       <c r="B50" s="68"/>
-      <c r="C50" s="70"/>
-      <c r="D50" s="9"/>
+      <c r="C50" s="70" t="s">
+        <v>563</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>553</v>
+      </c>
       <c r="E50" s="10"/>
       <c r="F50" s="13"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
       <c r="B51" s="68"/>
-      <c r="C51" s="70"/>
-      <c r="D51" s="9"/>
+      <c r="C51" s="70" t="s">
+        <v>562</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>554</v>
+      </c>
       <c r="E51" s="10"/>
       <c r="F51" s="13"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B52" s="68"/>
       <c r="C52" s="70"/>
       <c r="D52" s="9"/>
       <c r="E52" s="10"/>
       <c r="F52" s="13"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B53" s="68"/>
-      <c r="C53" s="70"/>
-      <c r="D53" s="9"/>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B53" s="68">
+        <v>14232</v>
+      </c>
+      <c r="C53" s="70">
+        <f t="shared" ref="C53" si="2">YEARFRAC($B$4,B53)</f>
+        <v>86.972222222222229</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>557</v>
+      </c>
       <c r="E53" s="10"/>
       <c r="F53" s="13"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B54" s="68"/>
-      <c r="C54" s="70"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="70" t="s">
+        <v>558</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>564</v>
+      </c>
       <c r="E54" s="10"/>
       <c r="F54" s="13"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B55" s="68"/>
-      <c r="C55" s="70"/>
+      <c r="C55" s="70" t="s">
+        <v>559</v>
+      </c>
       <c r="D55" s="9"/>
       <c r="E55" s="10"/>
       <c r="F55" s="13"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="68"/>
-      <c r="C56" s="70"/>
+      <c r="C56" s="70" t="s">
+        <v>560</v>
+      </c>
       <c r="D56" s="9"/>
       <c r="E56" s="10"/>
       <c r="F56" s="13"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B57" s="68"/>
-      <c r="C57" s="70"/>
-      <c r="D57" s="9"/>
+      <c r="C57" s="70" t="s">
+        <v>561</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>565</v>
+      </c>
       <c r="E57" s="10"/>
       <c r="F57" s="13"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B58" s="68"/>
-      <c r="C58" s="70"/>
+      <c r="C58" s="70" t="s">
+        <v>563</v>
+      </c>
       <c r="D58" s="9"/>
       <c r="E58" s="10"/>
       <c r="F58" s="13"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B59" s="68"/>
-      <c r="C59" s="70"/>
+      <c r="C59" s="70" t="s">
+        <v>562</v>
+      </c>
       <c r="D59" s="9"/>
       <c r="E59" s="10"/>
       <c r="F59" s="13"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B60" s="68"/>
       <c r="C60" s="70"/>
       <c r="D60" s="9"/>
       <c r="E60" s="10"/>
       <c r="F60" s="13"/>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B61" s="68"/>
       <c r="C61" s="70"/>
       <c r="D61" s="9"/>
       <c r="E61" s="10"/>
       <c r="F61" s="13"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B62" s="68"/>
       <c r="C62" s="70"/>
       <c r="D62" s="9"/>
       <c r="E62" s="10"/>
       <c r="F62" s="13"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B63" s="68"/>
       <c r="C63" s="70"/>
       <c r="D63" s="9"/>
       <c r="E63" s="10"/>
       <c r="F63" s="13"/>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B64" s="68"/>
       <c r="C64" s="70"/>
       <c r="D64" s="9"/>
@@ -4158,10 +4487,45 @@
       <c r="E107" s="10"/>
       <c r="F107" s="13"/>
     </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B108" s="68"/>
+      <c r="C108" s="70"/>
+      <c r="D108" s="9"/>
+      <c r="E108" s="10"/>
+      <c r="F108" s="13"/>
+    </row>
+    <row r="109" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B109" s="68"/>
+      <c r="C109" s="70"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="10"/>
+      <c r="F109" s="13"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B110" s="68"/>
+      <c r="C110" s="70"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="10"/>
+      <c r="F110" s="13"/>
+    </row>
+    <row r="111" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B111" s="68"/>
+      <c r="C111" s="70"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="10"/>
+      <c r="F111" s="13"/>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B112" s="68"/>
+      <c r="C112" s="70"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="10"/>
+      <c r="F112" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:F107" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F32">
-    <sortCondition ref="B7:B32"/>
+  <autoFilter ref="B6:F112" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:F37">
+    <sortCondition ref="B7:B37"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:F2"/>
@@ -4204,40 +4568,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="73">
+      <c r="B4" s="77">
         <f>MAX(B6:B390)</f>
-        <v>46059</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+        <v>46087</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -4252,25 +4616,25 @@
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -4281,19 +4645,19 @@
         <v>37</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -4307,16 +4671,16 @@
         <v>31</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>84</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>137</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -4330,10 +4694,10 @@
         <v>55</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>116</v>
@@ -4353,16 +4717,16 @@
         <v>55</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>116</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -4396,10 +4760,10 @@
         <v>37</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F12" s="14" t="s">
         <v>103</v>
@@ -4408,7 +4772,7 @@
         <v>34</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -4422,10 +4786,10 @@
         <v>51</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>23</v>
@@ -4528,19 +4892,19 @@
         <v>37</v>
       </c>
       <c r="D18" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="F18" s="11" t="s">
         <v>298</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>299</v>
       </c>
       <c r="G18" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -4575,7 +4939,7 @@
         <v>47</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>113</v>
@@ -4584,7 +4948,7 @@
         <v>34</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -4595,10 +4959,10 @@
         <v>37</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>22</v>
@@ -4616,7 +4980,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E22" s="10">
         <v>-23</v>
@@ -4659,7 +5023,7 @@
         <v>120</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
@@ -4668,7 +5032,7 @@
         <v>118</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -4702,10 +5066,10 @@
         <v>37</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>22</v>
@@ -4714,7 +5078,7 @@
         <v>118</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -4806,7 +5170,7 @@
         <v>133</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -4863,10 +5227,10 @@
         <v>37</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>113</v>
@@ -4884,17 +5248,17 @@
         <v>37</v>
       </c>
       <c r="D34" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>22</v>
       </c>
       <c r="G34" s="12"/>
       <c r="H34" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -4979,10 +5343,10 @@
       </c>
       <c r="F38" s="14"/>
       <c r="G38" s="14" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -5019,7 +5383,7 @@
         <v>86</v>
       </c>
       <c r="E40" s="27" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F40" s="14" t="s">
         <v>87</v>
@@ -5042,7 +5406,7 @@
         <v>86</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>85</v>
@@ -5051,7 +5415,7 @@
         <v>84</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -5161,7 +5525,7 @@
         <v>66</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="H46" s="13"/>
     </row>
@@ -5238,10 +5602,10 @@
         <v>37</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E50" s="30" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>22</v>
@@ -5259,19 +5623,19 @@
         <v>37</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F51" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="H51" s="13" t="s">
         <v>433</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -5305,10 +5669,10 @@
         <v>37</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E53" s="30" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>22</v>
@@ -5317,17 +5681,31 @@
         <v>34</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
+      <c r="B54" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>587</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>590</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>591</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" s="8"/>
@@ -5509,11 +5887,13 @@
     <hyperlink ref="E50" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
     <hyperlink ref="H45" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
     <hyperlink ref="E53" r:id="rId33" xr:uid="{F0164290-77DB-4F67-8C9C-2FE620F0B88B}"/>
+    <hyperlink ref="E54" r:id="rId34" xr:uid="{A2536E74-381F-407D-BF1C-5B8104BC2212}"/>
+    <hyperlink ref="F54" r:id="rId35" xr:uid="{20F5ECDA-AB98-424E-8FC8-923F99BE26E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId34"/>
-  <drawing r:id="rId35"/>
-  <legacyDrawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId36"/>
+  <drawing r:id="rId37"/>
+  <legacyDrawing r:id="rId38"/>
 </worksheet>
 </file>
 
@@ -5522,7 +5902,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -5547,42 +5927,42 @@
     </row>
     <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="73">
-        <f>MAX(B6:B347)</f>
-        <v>45968</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="B4" s="77">
+        <f>MAX(B6:B350)</f>
+        <v>46080</v>
+      </c>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
       <c r="I4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.25">
@@ -5598,25 +5978,25 @@
     <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -5643,25 +6023,25 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="8">
+      <c r="B8" s="31">
         <v>45033</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="36" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5688,400 +6068,400 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="8">
-        <v>45880</v>
+        <v>46080</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>429</v>
+        <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+        <v>583</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>84</v>
+      </c>
       <c r="H10" s="13" t="s">
-        <v>430</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
-        <v>45828</v>
+        <v>45880</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>354</v>
+        <v>427</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>385</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="13" t="s">
-        <v>384</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="8">
-        <v>45768</v>
+        <v>45828</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="G12" s="12"/>
+        <v>381</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>383</v>
+      </c>
       <c r="H12" s="13" t="s">
-        <v>357</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="8">
-        <v>45509</v>
+        <v>45768</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>442</v>
-      </c>
       <c r="F13" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B14" s="31">
+        <v>45509</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="E14" s="72" t="s">
+        <v>440</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="G14" s="73" t="s">
+        <v>313</v>
+      </c>
+      <c r="H14" s="36" t="s">
         <v>314</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="8">
-        <v>45768</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="13" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="8">
-        <v>45880</v>
+        <v>46080</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>425</v>
+        <v>352</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>440</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>427</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="8">
-        <v>45508</v>
+        <v>45768</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>318</v>
+        <v>356</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>84</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="G16" s="12"/>
       <c r="H16" s="13" t="s">
-        <v>320</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="8">
-        <v>45666</v>
+        <v>45880</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>317</v>
+        <v>424</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>344</v>
+        <v>423</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>312</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>370</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="8">
-        <v>45666</v>
+        <v>45508</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>317</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>341</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>84</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="8">
-        <v>45968</v>
+        <v>45666</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>471</v>
+        <v>315</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F19" s="11"/>
+        <v>316</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>342</v>
+      </c>
       <c r="G19" s="12" t="s">
-        <v>470</v>
+        <v>84</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="75" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="8">
-        <v>45831</v>
+        <v>45666</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>387</v>
+        <v>339</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>388</v>
-      </c>
-      <c r="H20" s="43" t="s">
-        <v>393</v>
+        <v>84</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="8">
-        <v>45828</v>
+        <v>45968</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>386</v>
+        <v>469</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>391</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>389</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="F21" s="11"/>
       <c r="G21" s="12" t="s">
-        <v>133</v>
+        <v>468</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="75" x14ac:dyDescent="0.2">
       <c r="B22" s="8">
-        <v>45790</v>
+        <v>45831</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>369</v>
+        <v>386</v>
+      </c>
+      <c r="H22" s="43" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="8">
-        <v>45889</v>
+        <v>45828</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E23" s="10"/>
+        <v>384</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>389</v>
+      </c>
       <c r="F23" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
+        <v>387</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="8">
-        <v>44606</v>
+        <v>45790</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>11</v>
+        <v>366</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>323</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="8">
-        <v>45505</v>
+        <v>45889</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>10</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="13"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
-        <v>45043</v>
+        <v>44606</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>16</v>
+        <v>319</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>11</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>15</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="8">
-        <v>45043</v>
+        <v>45505</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -6095,13 +6475,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>324</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>326</v>
+        <v>17</v>
+      </c>
+      <c r="F28" s="11">
+        <v>1059</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>16</v>
       </c>
       <c r="H28" s="13" t="s">
         <v>15</v>
@@ -6109,53 +6489,53 @@
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="8">
-        <v>45835</v>
+        <v>45043</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>329</v>
+        <v>17</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1059</v>
       </c>
       <c r="G29" s="12" t="s">
-        <v>346</v>
+        <v>16</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>424</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="8">
-        <v>45664</v>
+        <v>45043</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>345</v>
+        <v>322</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>347</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
-        <v>44661</v>
+        <v>45835</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>4</v>
@@ -6164,378 +6544,378 @@
         <v>5</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>343</v>
+        <v>401</v>
       </c>
       <c r="F31" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="G31" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="G31" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" s="13"/>
+      <c r="H31" s="13" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="8">
-        <v>43613</v>
+        <v>45664</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="E32" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>329</v>
-      </c>
       <c r="G32" s="12" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="8">
-        <v>43665</v>
+        <v>44661</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>327</v>
+        <v>5</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>332</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>333</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H33" s="13"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="8">
-        <v>45755</v>
+        <v>46069</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>306</v>
+        <v>5</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>307</v>
+        <v>567</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>308</v>
+        <v>568</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>309</v>
+        <v>569</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>310</v>
+        <v>570</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="8">
-        <v>45035</v>
+        <v>43613</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>307</v>
+        <v>325</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="8">
-        <v>45540</v>
+        <v>43665</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="8">
-        <v>45726</v>
+        <v>45755</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="8">
-        <v>45726</v>
+        <v>45035</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>305</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="8">
-        <v>45827</v>
+        <v>45540</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>377</v>
+        <v>333</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>379</v>
+        <v>334</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="8">
-        <v>45866</v>
+        <v>45726</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>409</v>
+        <v>299</v>
       </c>
       <c r="E40" s="30" t="s">
-        <v>422</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="12"/>
+        <v>574</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="H40" s="13" t="s">
-        <v>423</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
-        <v>45854</v>
+        <v>45726</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>398</v>
+        <v>299</v>
+      </c>
+      <c r="E41" s="30" t="s">
+        <v>574</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>410</v>
+        <v>302</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>411</v>
+        <v>191</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>415</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="8">
-        <v>45862</v>
+        <v>46073</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>419</v>
+        <v>299</v>
+      </c>
+      <c r="E42" s="30" t="s">
+        <v>574</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>417</v>
-      </c>
-      <c r="G42" s="12" t="s">
-        <v>418</v>
+        <v>575</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>576</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>415</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="8">
-        <v>45854</v>
+        <v>45827</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>409</v>
+        <v>299</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>412</v>
+        <v>375</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>414</v>
+        <v>376</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="8">
-        <v>45835</v>
+        <v>45866</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>399</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="F44" s="11"/>
+      <c r="G44" s="12"/>
       <c r="H44" s="13" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="8">
-        <v>45554</v>
+        <v>45854</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>9</v>
+        <v>407</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>8</v>
+        <v>396</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>6</v>
+        <v>408</v>
+      </c>
+      <c r="G45" s="12" t="s">
+        <v>409</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>5</v>
+        <v>413</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="44">
-        <v>45545</v>
-      </c>
-      <c r="C46" s="45" t="s">
+      <c r="B46" s="8">
+        <v>45862</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="46" t="s">
-        <v>339</v>
-      </c>
-      <c r="F46" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="H46" s="49" t="s">
-        <v>439</v>
+      <c r="D46" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="8">
-        <v>45887</v>
+        <v>45854</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>9</v>
+        <v>407</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>7</v>
+        <v>411</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>6</v>
+        <v>412</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>441</v>
+        <v>413</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -6546,56 +6926,112 @@
         <v>4</v>
       </c>
       <c r="D48" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="G48" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="8">
+        <v>45554</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="44">
+        <v>45545</v>
+      </c>
+      <c r="C50" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="F50" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G50" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H50" s="49" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="8">
+        <v>45887</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B52" s="8">
+        <v>45835</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="E48" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="G48" s="12" t="s">
+      <c r="G52" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H48" s="13" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="8"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="12"/>
-      <c r="H49" s="13"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="8"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="12"/>
-      <c r="H50" s="13"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="8"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="12"/>
-      <c r="H51" s="13"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="8"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="13"/>
+      <c r="H52" s="13" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="8"/>
@@ -6651,11 +7087,38 @@
       <c r="G58" s="12"/>
       <c r="H58" s="13"/>
     </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B59" s="8"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="13"/>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B60" s="8"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="13"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B61" s="8"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H48">
-    <sortCondition ref="D7:D48"/>
-    <sortCondition ref="E7:E48"/>
+  <autoFilter ref="B6:H20" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H52">
+    <sortCondition ref="D7:D52"/>
+    <sortCondition ref="E7:E52"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -6664,18 +7127,25 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{2B9393DA-1406-4AF5-9FF3-4B1125176216}"/>
-    <hyperlink ref="F25" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
-    <hyperlink ref="E34" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
-    <hyperlink ref="E12" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
-    <hyperlink ref="F14" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
-    <hyperlink ref="G43" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
-    <hyperlink ref="G42" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
-    <hyperlink ref="E40" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
-    <hyperlink ref="F15" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
-    <hyperlink ref="E35" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
+    <hyperlink ref="F27" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
+    <hyperlink ref="E37" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
+    <hyperlink ref="E13" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
+    <hyperlink ref="F16" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
+    <hyperlink ref="G47" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
+    <hyperlink ref="G46" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
+    <hyperlink ref="E44" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
+    <hyperlink ref="F17" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
+    <hyperlink ref="E38" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
+    <hyperlink ref="F14" r:id="rId11" xr:uid="{7A430EEE-2FA6-4E48-A07D-F8A23851554E}"/>
+    <hyperlink ref="E40" r:id="rId12" xr:uid="{9F1CCE38-CAEE-4F6A-9484-24259395663A}"/>
+    <hyperlink ref="E41" r:id="rId13" xr:uid="{935EA1D4-C322-424E-AB98-26A37ACBFD0A}"/>
+    <hyperlink ref="E42" r:id="rId14" xr:uid="{BD4220C7-5A56-4D7F-974D-8EB57638BC73}"/>
+    <hyperlink ref="E14" r:id="rId15" xr:uid="{2580999B-5C6F-4073-9DE9-8FA5F54BD22F}"/>
+    <hyperlink ref="F15" r:id="rId16" xr:uid="{BFB5DB6D-A181-4EC8-8608-FD327EA1ACEB}"/>
+    <hyperlink ref="E15" r:id="rId17" xr:uid="{75828819-0431-4CFA-9A6B-8CD02A0A0798}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -6709,40 +7179,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="73">
+      <c r="B4" s="77">
         <f>MAX(B6:B382)</f>
         <v>46058</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -6757,25 +7227,25 @@
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -6814,10 +7284,10 @@
         <v>31</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>28</v>
@@ -6838,16 +7308,16 @@
         <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="H9" s="13" t="s">
         <v>246</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6862,16 +7332,16 @@
         <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>84</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6886,16 +7356,16 @@
         <v>31</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="H11" s="13" t="s">
         <v>349</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6907,15 +7377,15 @@
         <v>32</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>165</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>166</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="12"/>
       <c r="H12" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6927,19 +7397,19 @@
         <v>32</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="F13" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="E13" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="F13" s="38" t="s">
+      <c r="G13" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="39" t="s">
-        <v>170</v>
-      </c>
       <c r="H13" s="13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6951,16 +7421,16 @@
         <v>32</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H14" s="13"/>
     </row>
@@ -6973,19 +7443,19 @@
         <v>32</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -6997,19 +7467,19 @@
         <v>32</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -7021,19 +7491,19 @@
         <v>32</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="H17" s="13" t="s">
         <v>251</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -7045,19 +7515,19 @@
         <v>32</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G18" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" s="13" t="s">
         <v>181</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -7069,17 +7539,17 @@
         <v>32</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="H19" s="13" t="s">
         <v>184</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -7091,17 +7561,17 @@
         <v>32</v>
       </c>
       <c r="D20" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="F20" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>188</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -7113,15 +7583,15 @@
         <v>32</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -7133,19 +7603,19 @@
         <v>32</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7157,19 +7627,19 @@
         <v>32</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E23" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>375</v>
-      </c>
       <c r="G23" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -7181,19 +7651,19 @@
         <v>32</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -7205,16 +7675,16 @@
         <v>32</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E25" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G25" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>254</v>
       </c>
       <c r="H25" s="13"/>
     </row>
@@ -7227,19 +7697,19 @@
         <v>32</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E26" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="G26" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="H26" s="13" t="s">
         <v>284</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -7251,19 +7721,19 @@
         <v>32</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="G27" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="G27" s="12" t="s">
-        <v>288</v>
-      </c>
       <c r="H27" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -7275,19 +7745,19 @@
         <v>32</v>
       </c>
       <c r="D28" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="F28" s="11" t="s">
+      <c r="G28" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="H28" s="13" t="s">
         <v>292</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7299,19 +7769,19 @@
         <v>32</v>
       </c>
       <c r="D29" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>190</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>191</v>
       </c>
       <c r="F29" s="11">
         <v>777</v>
       </c>
       <c r="G29" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="H29" s="13" t="s">
         <v>192</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -7323,19 +7793,19 @@
         <v>32</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F30" s="11">
         <v>777</v>
       </c>
       <c r="G30" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>192</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -7347,19 +7817,19 @@
         <v>32</v>
       </c>
       <c r="D31" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E31" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="F31" s="11">
         <v>777</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -7371,19 +7841,19 @@
         <v>32</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F32" s="11">
         <v>777</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -7395,14 +7865,14 @@
         <v>32</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H33" s="13"/>
     </row>
@@ -7415,19 +7885,19 @@
         <v>32</v>
       </c>
       <c r="D34" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>264</v>
       </c>
       <c r="F34" s="11">
         <v>777</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7439,19 +7909,19 @@
         <v>32</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F35" s="11">
         <v>777</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7463,19 +7933,19 @@
         <v>32</v>
       </c>
       <c r="D36" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="F36" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="G36" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="H36" s="13" t="s">
         <v>275</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7487,10 +7957,10 @@
         <v>32</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
@@ -7505,19 +7975,19 @@
         <v>32</v>
       </c>
       <c r="D38" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="F38" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="G38" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="G38" s="12" t="s">
+      <c r="H38" s="13" t="s">
         <v>197</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7529,19 +7999,19 @@
         <v>32</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E39" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>199</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="G39" s="12" t="s">
         <v>34</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -7553,10 +8023,10 @@
         <v>32</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>113</v>
@@ -7565,7 +8035,7 @@
         <v>34</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -7577,19 +8047,19 @@
         <v>32</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G41" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="H41" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="G41" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -7601,15 +8071,15 @@
         <v>32</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F42" s="11"/>
       <c r="G42" s="12"/>
       <c r="H42" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -7621,19 +8091,19 @@
         <v>32</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E43" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>206</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G43" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -7645,15 +8115,15 @@
         <v>32</v>
       </c>
       <c r="D44" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E44" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>209</v>
       </c>
       <c r="F44" s="11"/>
       <c r="G44" s="12"/>
       <c r="H44" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -7665,15 +8135,15 @@
         <v>32</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="F45" s="11"/>
       <c r="G45" s="12"/>
       <c r="H45" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -7685,15 +8155,15 @@
         <v>32</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>214</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="F46" s="11"/>
       <c r="G46" s="12"/>
       <c r="H46" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -7705,19 +8175,19 @@
         <v>32</v>
       </c>
       <c r="D47" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E47" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="F47" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="G47" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="G47" s="12" t="s">
-        <v>271</v>
-      </c>
       <c r="H47" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -7729,19 +8199,19 @@
         <v>32</v>
       </c>
       <c r="D48" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E48" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="F48" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G48" s="12" t="s">
+      <c r="H48" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -7753,16 +8223,16 @@
         <v>32</v>
       </c>
       <c r="D49" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>221</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>222</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H49" s="13"/>
     </row>
@@ -7774,19 +8244,19 @@
         <v>32</v>
       </c>
       <c r="D50" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -7797,16 +8267,16 @@
         <v>32</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H51" s="13"/>
     </row>
@@ -7818,16 +8288,16 @@
         <v>32</v>
       </c>
       <c r="D52" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="E52" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>7</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H52" s="13"/>
     </row>
@@ -7839,13 +8309,13 @@
         <v>32</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>30</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G53" s="12" t="s">
         <v>28</v>
@@ -7860,13 +8330,13 @@
         <v>32</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>28</v>
@@ -7881,19 +8351,19 @@
         <v>32</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E55" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="F55" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="G55" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="H55" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -7904,16 +8374,16 @@
         <v>32</v>
       </c>
       <c r="D56" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="E56" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="F56" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="G56" s="12" t="s">
         <v>241</v>
-      </c>
-      <c r="G56" s="12" t="s">
-        <v>242</v>
       </c>
       <c r="H56" s="13"/>
     </row>
@@ -7981,9 +8451,10 @@
     <hyperlink ref="F22" r:id="rId6" xr:uid="{C0FE7082-D516-494B-BA95-4A8387AFF75D}"/>
     <hyperlink ref="F23" r:id="rId7" xr:uid="{5917506B-1068-4DA5-89AA-F27F037AE325}"/>
     <hyperlink ref="E24" r:id="rId8" xr:uid="{24389F56-00DD-47EA-A8DC-02A43544EB26}"/>
+    <hyperlink ref="F39" r:id="rId9" xr:uid="{7AB2A455-9B10-4764-8D42-3CBA677B6EFB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -8013,38 +8484,38 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="73">
+      <c r="B4" s="77">
         <f>MAX(B6:B389)</f>
         <v>45965</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="50"/>
@@ -8060,32 +8531,32 @@
         <v>45965</v>
       </c>
       <c r="C7" s="60" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D7" s="61"/>
       <c r="E7" s="62"/>
       <c r="F7" s="56" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G7" s="53">
         <v>7.5</v>
       </c>
       <c r="H7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C8" s="63" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" s="64" t="s">
+        <v>462</v>
+      </c>
+      <c r="F8" s="65" t="s">
         <v>463</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>462</v>
-      </c>
-      <c r="E8" s="64" t="s">
-        <v>464</v>
-      </c>
-      <c r="F8" s="65" t="s">
-        <v>465</v>
       </c>
       <c r="G8" s="63"/>
     </row>
@@ -8094,10 +8565,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F9" s="56">
         <f>C9/$C$13</f>
@@ -8113,10 +8584,10 @@
         <v>7</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F10" s="56">
         <f t="shared" ref="F10:F12" si="0">C10/$C$13</f>
@@ -8132,10 +8603,10 @@
         <v>3</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F11" s="56">
         <f t="shared" si="0"/>
@@ -8151,10 +8622,10 @@
         <v>3</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F12" s="56">
         <f t="shared" si="0"/>
@@ -8223,40 +8694,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="71" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
+      <c r="B2" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="72" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
+      <c r="B3" s="76" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="73">
+      <c r="B4" s="77">
         <f>MAX(B6:B340)</f>
         <v>46040</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -8271,25 +8742,25 @@
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -8300,10 +8771,10 @@
         <v>43</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>40</v>
@@ -8324,7 +8795,7 @@
         <v>55</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>54</v>
@@ -8347,16 +8818,16 @@
         <v>55</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -8367,19 +8838,19 @@
         <v>43</v>
       </c>
       <c r="D10" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>491</v>
-      </c>
       <c r="H10" s="13" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -8393,13 +8864,13 @@
         <v>51</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>48</v>
@@ -8413,10 +8884,10 @@
         <v>43</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="12"/>
@@ -8451,14 +8922,14 @@
         <v>43</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H14" s="13"/>
     </row>
@@ -8470,10 +8941,10 @@
         <v>43</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="12"/>
@@ -8494,7 +8965,7 @@
         <v>40</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H16" s="13"/>
     </row>
@@ -8529,10 +9000,10 @@
         <v>43</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="12"/>
@@ -8549,14 +9020,14 @@
         <v>110</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="12"/>
       <c r="H19" s="13" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">

--- a/PARA EL RETIRO/ACCESOS VARIOS.xlsx
+++ b/PARA EL RETIRO/ACCESOS VARIOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zarkin-my.sharepoint.com/personal/it_due_zarkin_onmicrosoft_com/Documents/Documentos/al_maletin/PARA EL RETIRO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1259" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4E91E61-FA86-417C-A1B6-FD11E04FF6B2}"/>
+  <xr:revisionPtr revIDLastSave="1326" documentId="8_{1402AF8E-01AE-4905-A8E4-89E1DB17F1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F16CA44C-746E-4ADE-94CF-0DB821915AFD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{05E22A7C-AEF3-4E0A-857A-96523301D07D}"/>
   </bookViews>
   <sheets>
     <sheet name="FECHAS" sheetId="1" r:id="rId1"/>
@@ -19,23 +19,27 @@
     <sheet name="ITEKNIA" sheetId="3" r:id="rId4"/>
     <sheet name="VARIAS" sheetId="6" r:id="rId5"/>
     <sheet name="YOLANDA" sheetId="5" r:id="rId6"/>
+    <sheet name="ANA" sheetId="7" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">ANA!$B$6:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FECHAS!$B$6:$F$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ITEKNIA!$B$6:$H$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">VMA!$B$6:$H$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">YOLANDA!$B$6:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ZARKIN!$B$6:$H$22</definedName>
+    <definedName name="BANCOS" localSheetId="6">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="0">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="3">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="1">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="5">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS" localSheetId="2">[1]CATEGORIAS!$C$8:$C$20</definedName>
     <definedName name="BANCOS">[2]CATEGORIAS!$C$8:$C$20</definedName>
+    <definedName name="CATEGORIA" localSheetId="6">[1]CATEGORIAS!$B$6:$L$6</definedName>
     <definedName name="CATEGORIA" localSheetId="0">[1]CATEGORIAS!$B$6:$L$6</definedName>
     <definedName name="CATEGORIA" localSheetId="3">[1]CATEGORIAS!$B$6:$L$6</definedName>
     <definedName name="CATEGORIA" localSheetId="1">[1]CATEGORIAS!$B$6:$L$6</definedName>
@@ -144,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="605">
   <si>
     <t xml:space="preserve"> F5FMD RQGD7 22JHJ CNWMQ</t>
   </si>
@@ -1903,9 +1907,6 @@
     <t>1 385 635 956</t>
   </si>
   <si>
-    <t>Equipo DELL</t>
-  </si>
-  <si>
     <t>Maquina proporcionada por Zarkin.</t>
   </si>
   <si>
@@ -1928,6 +1929,48 @@
   </si>
   <si>
     <t>Manez107</t>
+  </si>
+  <si>
+    <t>39 00 72</t>
+  </si>
+  <si>
+    <t>Equipo DELL ZARKIN</t>
+  </si>
+  <si>
+    <t>RUSTDESK</t>
+  </si>
+  <si>
+    <t>214 142 418</t>
+  </si>
+  <si>
+    <t>317 879 699</t>
+  </si>
+  <si>
+    <t>Escritorio Remoto del 1014</t>
+  </si>
+  <si>
+    <t>https://www.freecodecamp.org/</t>
+  </si>
+  <si>
+    <t>FREECODE</t>
+  </si>
+  <si>
+    <t>Inicio Python</t>
+  </si>
+  <si>
+    <t>Macro 130</t>
+  </si>
+  <si>
+    <t>Exclusiva de Diseño.</t>
+  </si>
+  <si>
+    <t>Dan$2022</t>
+  </si>
+  <si>
+    <t>45.239.78.35:1014</t>
+  </si>
+  <si>
+    <t>Cambio de IP por cancelacion con TotalPlay.</t>
   </si>
 </sst>
 </file>
@@ -1939,7 +1982,7 @@
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2061,8 +2104,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2096,6 +2151,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2140,7 +2201,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2340,14 +2401,50 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2358,6 +2455,9 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2516,13 +2616,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>286481</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>585</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2560,13 +2660,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>657919</xdr:colOff>
-      <xdr:row>50</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>57690</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2729,6 +2829,93 @@
     </xdr:pic>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>885825</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="990600" cy="981075"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="image2.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{911A2E33-CFF9-45D3-BD13-4273743C1DEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1133475" y="85725"/>
+          <a:ext cx="990600" cy="981075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>242458</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>8659</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>567287</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>45421</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2EEF613-296E-9C2F-1805-65536CD0A528}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="528208" y="4087091"/>
+          <a:ext cx="2913897" cy="5180262"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3324,33 +3511,33 @@
     </row>
     <row r="2" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
     </row>
     <row r="3" spans="1:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
     </row>
     <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="77">
+      <c r="B4" s="89">
         <v>45999</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="89"/>
     </row>
     <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -4568,40 +4755,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="77">
+      <c r="B4" s="89">
         <f>MAX(B6:B390)</f>
-        <v>46087</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+        <v>46125</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -4680,7 +4867,7 @@
         <v>84</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -4991,53 +5178,53 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="8">
-        <v>44564</v>
-      </c>
-      <c r="C23" s="9" t="s">
+        <v>46125</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="11" t="s">
+        <v>598</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>121</v>
+      <c r="G23" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="8">
-        <v>44215</v>
+        <v>44564</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>277</v>
+        <v>123</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>278</v>
+        <v>34</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="8">
-        <v>44958</v>
+        <v>44215</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>37</v>
@@ -5045,68 +5232,68 @@
       <c r="D25" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>119</v>
+      <c r="E25" s="10" t="s">
+        <v>277</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="12" t="s">
         <v>118</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>117</v>
+        <v>278</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
-        <v>45782</v>
+        <v>44958</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>362</v>
+        <v>120</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="14" t="s">
         <v>118</v>
       </c>
       <c r="H26" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="8">
+        <v>45782</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E27" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>363</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="31">
-        <v>45335</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="E27" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="H27" s="36" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="31">
-        <v>45663</v>
+        <v>45335</v>
       </c>
       <c r="C28" s="32" t="s">
         <v>37</v>
@@ -5117,42 +5304,42 @@
       <c r="E28" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="37" t="s">
         <v>113</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H28" s="36" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" s="8">
-        <v>45740</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="31">
+        <v>45663</v>
+      </c>
+      <c r="C29" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="34" t="s">
         <v>113</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="13" t="s">
+      <c r="G29" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="36" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="8">
-        <v>45828</v>
+        <v>45740</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>37</v>
@@ -5167,489 +5354,491 @@
         <v>113</v>
       </c>
       <c r="G30" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B31" s="8">
+        <v>45828</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H31" s="13" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B31" s="16">
-        <v>45127</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="16">
-        <v>45014</v>
+        <v>45127</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="28" t="s">
-        <v>102</v>
+        <v>107</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="8">
-        <v>45847</v>
+      <c r="B33" s="16">
+        <v>45014</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>406</v>
+        <v>105</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>104</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H33" s="13"/>
+        <v>103</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="8">
+        <v>45847</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="8">
         <v>45671</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C35" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D35" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E35" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F35" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G34" s="12"/>
-      <c r="H34" s="13" t="s">
+      <c r="G35" s="12"/>
+      <c r="H35" s="13" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B35" s="40">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="40">
         <v>44620</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C36" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="36" t="s">
+      <c r="D36" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E36" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F36" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="G36" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="H35" s="36" t="s">
+      <c r="H36" s="36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36" s="16">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="16">
         <v>45318</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C37" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D37" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E37" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F37" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G36" s="18" t="s">
+      <c r="G37" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H37" s="13" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B37" s="31">
-        <v>44967</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E37" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" s="36" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="8">
+        <v>46087</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="E38" s="30" t="s">
+        <v>586</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="31">
+        <v>44967</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="H39" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="8">
         <v>46059</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B39" s="8">
-        <v>45232</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="H39" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B40" s="16">
-        <v>44851</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E40" s="27" t="s">
-        <v>484</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>49</v>
+      <c r="D40" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14" t="s">
+        <v>524</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>83</v>
+        <v>525</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41" s="16">
-        <v>45846</v>
+      <c r="B41" s="8">
+        <v>45232</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>484</v>
+      <c r="D41" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>84</v>
+        <v>90</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>89</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>404</v>
+        <v>88</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="16">
-        <v>44930</v>
-      </c>
-      <c r="C42" s="13" t="s">
+        <v>44851</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>80</v>
+      <c r="D42" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>484</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="16">
+        <v>45846</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>484</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="16">
         <v>44930</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C44" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D44" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E44" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F44" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="G43" s="18" t="s">
+      <c r="G44" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H43" s="13" t="s">
+      <c r="H44" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="16">
+        <v>44930</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44" s="8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="8">
         <v>45362</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C46" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D46" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E46" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F46" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G46" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="H44" s="13" t="s">
+      <c r="H46" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="8">
         <v>45161</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C47" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D47" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E47" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F47" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G45" s="14"/>
-      <c r="H45" s="27" t="s">
+      <c r="G47" s="14"/>
+      <c r="H47" s="27" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="16">
-        <v>45488</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F46" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="16">
-        <v>44958</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="F47" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H47" s="13"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="16">
-        <v>45120</v>
+        <v>45488</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>64</v>
+        <v>68</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>67</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>62</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="H48" s="13"/>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="8">
-        <v>45310</v>
-      </c>
-      <c r="C49" s="9" t="s">
+      <c r="B49" s="16">
+        <v>44958</v>
+      </c>
+      <c r="C49" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>60</v>
+        <v>68</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>70</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="14"/>
-      <c r="H49" s="13" t="s">
-        <v>59</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="13"/>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="8">
-        <v>45863</v>
+      <c r="B50" s="16">
+        <v>45120</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="E50" s="30" t="s">
-        <v>418</v>
+        <v>65</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>64</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G50" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="13"/>
+        <v>63</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="8">
-        <v>41918</v>
-      </c>
-      <c r="C51" s="13" t="s">
+        <v>45310</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>37</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>434</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>431</v>
-      </c>
-      <c r="G51" s="14" t="s">
-        <v>432</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F51" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" s="14"/>
       <c r="H51" s="13" t="s">
-        <v>433</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B52" s="16">
-        <v>44927</v>
+      <c r="B52" s="8">
+        <v>46055</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52" s="26" t="s">
-        <v>57</v>
+        <v>521</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>522</v>
       </c>
       <c r="F52" s="14" t="s">
         <v>22</v>
@@ -5658,63 +5847,75 @@
         <v>34</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>56</v>
+        <v>523</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" s="8">
-        <v>46055</v>
+        <v>45863</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>521</v>
+        <v>419</v>
       </c>
       <c r="E53" s="30" t="s">
-        <v>522</v>
+        <v>418</v>
       </c>
       <c r="F53" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="G53" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>523</v>
-      </c>
+      <c r="G53" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" s="8">
-        <v>46087</v>
+        <v>41918</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>37</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>588</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>587</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>590</v>
+        <v>435</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>431</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>591</v>
+        <v>432</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>589</v>
+        <v>433</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
+      <c r="B55" s="16">
+        <v>44927</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" s="8"/>
@@ -5844,9 +6045,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B6:H69" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H52">
-    <sortCondition ref="D7:D52"/>
-    <sortCondition ref="E7:E52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H55">
+    <sortCondition ref="D7:D55"/>
+    <sortCondition ref="E7:E55"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -5857,38 +6058,38 @@
     <hyperlink ref="E12" r:id="rId1" xr:uid="{15C086F2-F597-4D51-B2E7-3FAD96221D78}"/>
     <hyperlink ref="E13" r:id="rId2" xr:uid="{8BB978DC-E232-48F0-9939-636AAC0E6406}"/>
     <hyperlink ref="F16" r:id="rId3" xr:uid="{92544A31-8743-4333-B41A-FC5AFE5A1056}"/>
-    <hyperlink ref="F27" r:id="rId4" xr:uid="{82D17D54-F1FB-4528-8C20-0FDDE784D3DA}"/>
+    <hyperlink ref="F28" r:id="rId4" xr:uid="{82D17D54-F1FB-4528-8C20-0FDDE784D3DA}"/>
     <hyperlink ref="E17" r:id="rId5" xr:uid="{EAA12730-E964-4FF6-8B15-29788EDF5E5A}"/>
     <hyperlink ref="H17" r:id="rId6" xr:uid="{6126EC3D-FD40-4669-A1D5-C19D1CA3EBFE}"/>
-    <hyperlink ref="E32" r:id="rId7" xr:uid="{DC0A551E-2043-4838-8B1D-E6890D4FF633}"/>
-    <hyperlink ref="H32" r:id="rId8" xr:uid="{AF14144D-3EEB-40CC-BAC6-8BA7FEAC55F2}"/>
-    <hyperlink ref="E47" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
-    <hyperlink ref="E48" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
-    <hyperlink ref="E52" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
+    <hyperlink ref="E33" r:id="rId7" xr:uid="{DC0A551E-2043-4838-8B1D-E6890D4FF633}"/>
+    <hyperlink ref="H33" r:id="rId8" xr:uid="{AF14144D-3EEB-40CC-BAC6-8BA7FEAC55F2}"/>
+    <hyperlink ref="E49" r:id="rId9" xr:uid="{C6C76AED-9C33-4108-B05F-F32A6AE08B52}"/>
+    <hyperlink ref="E50" r:id="rId10" xr:uid="{D5A0A6EC-E5D8-4323-869A-4E084BD0B677}"/>
+    <hyperlink ref="E55" r:id="rId11" xr:uid="{69E6FD0B-CCBB-4BB0-9A43-EAB0015DCE11}"/>
     <hyperlink ref="E10" r:id="rId12" xr:uid="{2A9A4DB1-04E3-4AEC-9748-2C41FBA8890F}"/>
-    <hyperlink ref="E35" r:id="rId13" xr:uid="{F7C616EB-3A49-4692-9217-779F9011DE23}"/>
-    <hyperlink ref="F35" r:id="rId14" xr:uid="{4B10E67E-EC62-43AA-877D-FB5D2D4285F6}"/>
-    <hyperlink ref="E42" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
-    <hyperlink ref="F39" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
-    <hyperlink ref="E43" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
-    <hyperlink ref="E49" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
-    <hyperlink ref="E36" r:id="rId19" xr:uid="{89E68C26-BCFC-43A5-BFA4-A8E225383626}"/>
-    <hyperlink ref="F36" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
+    <hyperlink ref="E36" r:id="rId13" xr:uid="{F7C616EB-3A49-4692-9217-779F9011DE23}"/>
+    <hyperlink ref="F36" r:id="rId14" xr:uid="{4B10E67E-EC62-43AA-877D-FB5D2D4285F6}"/>
+    <hyperlink ref="E44" r:id="rId15" xr:uid="{0BF73A89-B92E-425A-898F-37C7CBF042F2}"/>
+    <hyperlink ref="F41" r:id="rId16" xr:uid="{B9116BFB-CDC1-45BA-8013-DFA7870403F1}"/>
+    <hyperlink ref="E45" r:id="rId17" xr:uid="{C6309289-8973-412F-B925-7C6256933BAE}"/>
+    <hyperlink ref="E51" r:id="rId18" xr:uid="{43D3E767-84D7-4B69-8536-7BE78B4A52EE}"/>
+    <hyperlink ref="E37" r:id="rId19" xr:uid="{89E68C26-BCFC-43A5-BFA4-A8E225383626}"/>
+    <hyperlink ref="F37" r:id="rId20" xr:uid="{C2258EE3-C9B0-4308-ACF5-D68174432934}"/>
     <hyperlink ref="E15" r:id="rId21" xr:uid="{24B9D316-C43F-4E45-A3FC-348F1BC5501D}"/>
     <hyperlink ref="F15" r:id="rId22" xr:uid="{CBCE9FA7-4504-4520-B59C-D974CE2099B7}"/>
-    <hyperlink ref="E46" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
-    <hyperlink ref="F28" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
+    <hyperlink ref="E48" r:id="rId23" xr:uid="{882B7AAD-BDFB-4447-9C2B-52348FBCD628}"/>
+    <hyperlink ref="F29" r:id="rId24" xr:uid="{8A6EA065-B212-4D58-A0AD-E8262CF84E9F}"/>
     <hyperlink ref="F11" r:id="rId25" xr:uid="{16FC9D2A-4AC9-4E47-9F68-1F6F2F32790A}"/>
     <hyperlink ref="H18" r:id="rId26" display="vcuevar@gmail.com" xr:uid="{2BC56FD7-7E2B-4127-AFB2-59B9E06C1F4A}"/>
-    <hyperlink ref="F29" r:id="rId27" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
-    <hyperlink ref="E26" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
-    <hyperlink ref="F30" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
-    <hyperlink ref="F33" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
-    <hyperlink ref="E50" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
-    <hyperlink ref="H45" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
-    <hyperlink ref="E53" r:id="rId33" xr:uid="{F0164290-77DB-4F67-8C9C-2FE620F0B88B}"/>
-    <hyperlink ref="E54" r:id="rId34" xr:uid="{A2536E74-381F-407D-BF1C-5B8104BC2212}"/>
-    <hyperlink ref="F54" r:id="rId35" xr:uid="{20F5ECDA-AB98-424E-8FC8-923F99BE26E1}"/>
+    <hyperlink ref="F30" r:id="rId27" xr:uid="{9CB92F39-AC9F-45F8-AC0B-1815A7C53A4A}"/>
+    <hyperlink ref="E27" r:id="rId28" xr:uid="{0EF4AF42-0D81-447F-93B9-DF4FCF6D4CC6}"/>
+    <hyperlink ref="F31" r:id="rId29" xr:uid="{017BC6FC-67D7-4A13-A0A6-7BD83821710D}"/>
+    <hyperlink ref="F34" r:id="rId30" xr:uid="{3D286E06-8871-42A2-8A69-3DAB4BED248A}"/>
+    <hyperlink ref="E53" r:id="rId31" xr:uid="{1A05DF65-48E0-4812-9365-0C481CDA4F9A}"/>
+    <hyperlink ref="H47" r:id="rId32" xr:uid="{28AB7F00-43CA-4D59-9E39-1B0D8D6C343F}"/>
+    <hyperlink ref="E52" r:id="rId33" xr:uid="{F0164290-77DB-4F67-8C9C-2FE620F0B88B}"/>
+    <hyperlink ref="E38" r:id="rId34" xr:uid="{A2536E74-381F-407D-BF1C-5B8104BC2212}"/>
+    <hyperlink ref="F38" r:id="rId35" xr:uid="{20F5ECDA-AB98-424E-8FC8-923F99BE26E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId36"/>
@@ -5902,7 +6103,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0066"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" customWidth="1"/>
@@ -5927,40 +6128,40 @@
     </row>
     <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="77">
-        <f>MAX(B6:B350)</f>
-        <v>46080</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="B4" s="89">
+        <f>MAX(B6:B354)</f>
+        <v>46126</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
       <c r="I4" t="s">
         <v>369</v>
       </c>
@@ -6023,25 +6224,25 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="31">
+      <c r="B8" s="73">
         <v>45033</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="78" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6077,7 +6278,7 @@
         <v>31</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>582</v>
@@ -6086,98 +6287,100 @@
         <v>84</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="8">
-        <v>45880</v>
+        <v>46121</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>427</v>
+        <v>593</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="12"/>
+        <v>592</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>594</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="H11" s="13" t="s">
-        <v>428</v>
+        <v>583</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="8">
-        <v>45828</v>
+        <v>46122</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>352</v>
+        <v>593</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>380</v>
+        <v>326</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>381</v>
+        <v>595</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>382</v>
+        <v>596</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="8">
-        <v>45768</v>
+        <v>45880</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>352</v>
+        <v>427</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>353</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="F13" s="11"/>
       <c r="G13" s="12"/>
       <c r="H13" s="13" t="s">
-        <v>355</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="31">
-        <v>45509</v>
-      </c>
-      <c r="C14" s="32" t="s">
+      <c r="B14" s="8">
+        <v>45828</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="E14" s="72" t="s">
-        <v>440</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="G14" s="73" t="s">
-        <v>313</v>
-      </c>
-      <c r="H14" s="36" t="s">
-        <v>314</v>
+      <c r="E14" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>383</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="8">
-        <v>46080</v>
+        <v>45768</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>4</v>
@@ -6185,829 +6388,827 @@
       <c r="D15" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B16" s="31">
+        <v>45509</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="E16" s="71" t="s">
         <v>440</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F16" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="G15" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B16" s="8">
-        <v>45768</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="13" t="s">
-        <v>358</v>
+      <c r="G16" s="72" t="s">
+        <v>313</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="8">
-        <v>45880</v>
+        <v>46080</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>423</v>
+        <v>352</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>440</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>312</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>425</v>
+        <v>585</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="8">
-        <v>45508</v>
+        <v>45768</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>315</v>
+        <v>352</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>84</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="G18" s="12"/>
       <c r="H18" s="13" t="s">
-        <v>318</v>
+        <v>358</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="8">
-        <v>45666</v>
+        <v>45880</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F19" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="31">
+        <v>45508</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E20" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F20" s="90" t="s">
+        <v>317</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="31">
+        <v>45666</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="F21" s="90" t="s">
         <v>342</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G21" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H21" s="36" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B20" s="8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="31">
         <v>45666</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C22" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D22" s="32" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E22" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F22" s="90" t="s">
         <v>339</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G22" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H22" s="36" t="s">
         <v>340</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B21" s="8">
-        <v>45968</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="75" x14ac:dyDescent="0.2">
-      <c r="B22" s="8">
-        <v>45831</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="H22" s="43" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="8">
-        <v>45828</v>
+        <v>46126</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>389</v>
+        <v>603</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>388</v>
+        <v>604</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="8">
-        <v>45790</v>
+        <v>45968</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>364</v>
+        <v>469</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>342</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>366</v>
+        <v>468</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="75" x14ac:dyDescent="0.2">
       <c r="B25" s="8">
-        <v>45889</v>
+        <v>45831</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E25" s="10"/>
+        <v>384</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>389</v>
+      </c>
       <c r="F25" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
+        <v>385</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="H25" s="43" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="8">
-        <v>44606</v>
+        <v>45828</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>14</v>
+        <v>384</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>319</v>
+        <v>389</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>321</v>
+        <v>388</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="8">
-        <v>45505</v>
+        <v>45790</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>11</v>
+        <v>365</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>10</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="8">
-        <v>45043</v>
+        <v>46125</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>18</v>
+        <v>364</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>16</v>
+        <v>600</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>366</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>15</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="8">
-        <v>45043</v>
+        <v>45889</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="11">
-        <v>1059</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>15</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="E29" s="10"/>
+      <c r="F29" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="13"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="8">
-        <v>45043</v>
+        <v>44606</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>324</v>
+        <v>11</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>15</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="8">
-        <v>45835</v>
+        <v>45505</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F31" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>344</v>
+        <v>13</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>11</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>422</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="8">
-        <v>45664</v>
+        <v>45043</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="F32" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>344</v>
+        <v>17</v>
+      </c>
+      <c r="F32" s="11">
+        <v>1059</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>16</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>345</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="8">
-        <v>44661</v>
+        <v>45043</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>342</v>
+        <v>17</v>
+      </c>
+      <c r="F33" s="11">
+        <v>1059</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="H33" s="13"/>
+        <v>16</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="8">
-        <v>46069</v>
+        <v>45043</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>567</v>
+        <v>322</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>568</v>
+        <v>323</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>569</v>
+        <v>324</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>570</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="8">
-        <v>43613</v>
+        <v>45835</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>326</v>
+        <v>401</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>327</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>329</v>
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="8">
-        <v>43665</v>
+        <v>45664</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>325</v>
+        <v>5</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>327</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="8">
-        <v>45755</v>
+        <v>44661</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>304</v>
+        <v>5</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>307</v>
-      </c>
-      <c r="H37" s="13" t="s">
-        <v>308</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="H37" s="13"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="8">
-        <v>45035</v>
+        <v>46069</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>305</v>
+        <v>5</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>567</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>306</v>
+        <v>568</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>307</v>
+        <v>569</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>308</v>
+        <v>570</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="8">
-        <v>45540</v>
+        <v>43613</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="8">
-        <v>45726</v>
+        <v>43665</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>574</v>
+        <v>325</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>326</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>191</v>
+        <v>330</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="8">
-        <v>45726</v>
+        <v>45755</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>574</v>
+        <v>304</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>305</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>191</v>
+        <v>307</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="8">
-        <v>46073</v>
+        <v>45035</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E42" s="30" t="s">
-        <v>574</v>
+        <v>305</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="G42" s="14" t="s">
-        <v>576</v>
+        <v>306</v>
+      </c>
+      <c r="G42" s="12" t="s">
+        <v>307</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>577</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="8">
-        <v>45827</v>
+        <v>45540</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>299</v>
+        <v>332</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>375</v>
+        <v>333</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="G43" s="14" t="s">
-        <v>377</v>
+        <v>334</v>
+      </c>
+      <c r="G43" s="12" t="s">
+        <v>335</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="8">
-        <v>45866</v>
+        <v>45726</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>407</v>
+        <v>299</v>
       </c>
       <c r="E44" s="30" t="s">
-        <v>420</v>
-      </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="12"/>
+        <v>574</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="G44" s="12" t="s">
+        <v>191</v>
+      </c>
       <c r="H44" s="13" t="s">
-        <v>421</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="8">
-        <v>45854</v>
+        <v>45726</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>396</v>
+        <v>299</v>
+      </c>
+      <c r="E45" s="30" t="s">
+        <v>574</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>408</v>
+        <v>302</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>409</v>
+        <v>191</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>413</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="8">
-        <v>45862</v>
+        <v>46073</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>417</v>
+        <v>299</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>574</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="G46" s="12" t="s">
-        <v>416</v>
+        <v>575</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>576</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>413</v>
+        <v>577</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="8">
-        <v>45854</v>
+        <v>45827</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>407</v>
+        <v>299</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>412</v>
+        <v>376</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>377</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>413</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="8">
-        <v>45835</v>
+        <v>45866</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>397</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="E48" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="F48" s="11"/>
+      <c r="G48" s="12"/>
       <c r="H48" s="13" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="8">
-        <v>45554</v>
+        <v>45854</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>9</v>
+        <v>407</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>8</v>
+        <v>396</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G49" s="14" t="s">
-        <v>6</v>
+        <v>408</v>
+      </c>
+      <c r="G49" s="12" t="s">
+        <v>409</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>5</v>
+        <v>413</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="44">
-        <v>45545</v>
-      </c>
-      <c r="C50" s="45" t="s">
+      <c r="B50" s="8">
+        <v>45862</v>
+      </c>
+      <c r="C50" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="46" t="s">
-        <v>337</v>
-      </c>
-      <c r="F50" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="G50" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="H50" s="49" t="s">
-        <v>437</v>
+      <c r="D50" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" s="8">
-        <v>45887</v>
+        <v>45854</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>9</v>
+        <v>407</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>438</v>
+        <v>410</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>7</v>
+        <v>411</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>6</v>
+        <v>412</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -7018,56 +7219,112 @@
         <v>4</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>6</v>
+        <v>397</v>
       </c>
       <c r="H52" s="13" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="13"/>
+      <c r="B53" s="8">
+        <v>45554</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B54" s="8"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="13"/>
+      <c r="B54" s="44">
+        <v>45545</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="F54" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="G54" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="49" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="13"/>
+      <c r="B55" s="8">
+        <v>45887</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B56" s="8"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="13"/>
+      <c r="B56" s="8">
+        <v>45835</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="G56" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="8"/>
@@ -7114,11 +7371,47 @@
       <c r="G61" s="12"/>
       <c r="H61" s="13"/>
     </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B62" s="8"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="13"/>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B63" s="8"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="11"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="13"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B64" s="8"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="13"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B65" s="8"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="13"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B6:H20" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H52">
-    <sortCondition ref="D7:D52"/>
-    <sortCondition ref="E7:E52"/>
+  <autoFilter ref="B6:H22" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B7:H56">
+    <sortCondition ref="D7:D56"/>
+    <sortCondition ref="E7:E56"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:H2"/>
@@ -7127,22 +7420,22 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H7" r:id="rId1" xr:uid="{2B9393DA-1406-4AF5-9FF3-4B1125176216}"/>
-    <hyperlink ref="F27" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
-    <hyperlink ref="E37" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
-    <hyperlink ref="E13" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
-    <hyperlink ref="F16" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
-    <hyperlink ref="G47" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
-    <hyperlink ref="G46" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
-    <hyperlink ref="E44" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
-    <hyperlink ref="F17" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
-    <hyperlink ref="E38" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
-    <hyperlink ref="F14" r:id="rId11" xr:uid="{7A430EEE-2FA6-4E48-A07D-F8A23851554E}"/>
-    <hyperlink ref="E40" r:id="rId12" xr:uid="{9F1CCE38-CAEE-4F6A-9484-24259395663A}"/>
-    <hyperlink ref="E41" r:id="rId13" xr:uid="{935EA1D4-C322-424E-AB98-26A37ACBFD0A}"/>
-    <hyperlink ref="E42" r:id="rId14" xr:uid="{BD4220C7-5A56-4D7F-974D-8EB57638BC73}"/>
-    <hyperlink ref="E14" r:id="rId15" xr:uid="{2580999B-5C6F-4073-9DE9-8FA5F54BD22F}"/>
-    <hyperlink ref="F15" r:id="rId16" xr:uid="{BFB5DB6D-A181-4EC8-8608-FD327EA1ACEB}"/>
-    <hyperlink ref="E15" r:id="rId17" xr:uid="{75828819-0431-4CFA-9A6B-8CD02A0A0798}"/>
+    <hyperlink ref="F31" r:id="rId2" xr:uid="{5B237A66-5FDE-4792-A467-F5CF07D5DCC1}"/>
+    <hyperlink ref="E41" r:id="rId3" xr:uid="{F409CE32-EBE8-4BE9-B305-3F871B965A46}"/>
+    <hyperlink ref="E15" r:id="rId4" display="zarkinsoporte@gmail.com" xr:uid="{2A7B02A3-3463-45FA-AE4B-C33F6CF7FA15}"/>
+    <hyperlink ref="F18" r:id="rId5" xr:uid="{E3462E40-C391-4B83-8473-009ED89E7CEE}"/>
+    <hyperlink ref="G51" r:id="rId6" xr:uid="{A009C80D-5058-4AFD-9D0B-55B518C466B9}"/>
+    <hyperlink ref="G50" r:id="rId7" display="Zarkin@2025" xr:uid="{917C7D59-7AFC-418D-B624-A9A855335A83}"/>
+    <hyperlink ref="E48" r:id="rId8" xr:uid="{0331E833-D86E-4B37-A89F-9FBF09AD7385}"/>
+    <hyperlink ref="F19" r:id="rId9" xr:uid="{202FA394-F494-410C-A882-D2CFF22984C4}"/>
+    <hyperlink ref="E42" r:id="rId10" xr:uid="{FA9891FC-1642-4FC7-8837-71D5A2C598B9}"/>
+    <hyperlink ref="F16" r:id="rId11" xr:uid="{7A430EEE-2FA6-4E48-A07D-F8A23851554E}"/>
+    <hyperlink ref="E44" r:id="rId12" xr:uid="{9F1CCE38-CAEE-4F6A-9484-24259395663A}"/>
+    <hyperlink ref="E45" r:id="rId13" xr:uid="{935EA1D4-C322-424E-AB98-26A37ACBFD0A}"/>
+    <hyperlink ref="E46" r:id="rId14" xr:uid="{BD4220C7-5A56-4D7F-974D-8EB57638BC73}"/>
+    <hyperlink ref="E16" r:id="rId15" xr:uid="{2580999B-5C6F-4073-9DE9-8FA5F54BD22F}"/>
+    <hyperlink ref="F17" r:id="rId16" xr:uid="{BFB5DB6D-A181-4EC8-8608-FD327EA1ACEB}"/>
+    <hyperlink ref="E17" r:id="rId17" xr:uid="{75828819-0431-4CFA-9A6B-8CD02A0A0798}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId18"/>
@@ -7179,40 +7472,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="77">
+      <c r="B4" s="89">
         <f>MAX(B6:B382)</f>
-        <v>46058</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+        <v>46120</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -7250,32 +7543,32 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="8">
+      <c r="B7" s="80">
         <v>45604</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="85" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="8">
-        <v>45604</v>
+        <v>46120</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>32</v>
@@ -8484,38 +8777,38 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="2:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B4" s="77">
+      <c r="B4" s="89">
         <f>MAX(B6:B389)</f>
         <v>45965</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
     </row>
     <row r="5" spans="2:8" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="50"/>
@@ -8694,40 +8987,40 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
     </row>
     <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="88" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="77">
+      <c r="B4" s="89">
         <f>MAX(B6:B340)</f>
         <v>46040</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
     </row>
     <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -9097,4 +9390,281 @@
   <pageSetup scale="88" orientation="landscape" r:id="rId7"/>
   <drawing r:id="rId8"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74E6686-DD28-4DAA-AA89-7D6727EDA624}">
+  <sheetPr>
+    <tabColor rgb="FFFF0066"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.21875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="2"/>
+      <c r="B2" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="87"/>
+    </row>
+    <row r="3" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="88" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="87"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="87"/>
+      <c r="F3" s="87"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+      <c r="B4" s="89">
+        <f>MAX(B6:B340)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="87"/>
+      <c r="D4" s="87"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+    </row>
+    <row r="5" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="8"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="13"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="8"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="8"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="13"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="8"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="8"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="13"/>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="79" t="s">
+        <v>591</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21" s="8"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="13"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24" s="8"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="13"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B6:H19" xr:uid="{C59BC6B0-8656-4FE4-8198-8FB66AA2275D}"/>
+  <mergeCells count="3">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="88" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>